--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 млрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7C8E0D-AEB0-485F-B0B3-D5791F2C18BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AC8E6F-E854-45D3-BBCC-02B5E77B3CA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$107</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -644,8 +644,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -781,7 +782,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -807,6 +808,8 @@
     <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -5541,7 +5544,8 @@
     <col min="22" max="31" width="6" customWidth="1"/>
     <col min="32" max="32" width="53.85546875" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="50" width="8" customWidth="1"/>
+    <col min="34" max="34" width="8" style="26" customWidth="1"/>
+    <col min="35" max="50" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -5578,7 +5582,7 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
+      <c r="AH1" s="25"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
@@ -5630,7 +5634,7 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
+      <c r="AH2" s="25"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
@@ -5748,7 +5752,7 @@
       <c r="AG3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AH3" s="1"/>
+      <c r="AH3" s="25"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
+      <c r="AH4" s="25"/>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
@@ -5946,7 +5950,7 @@
         <f>SUM(AG6:AG499)</f>
         <v>5578.4400000000005</v>
       </c>
-      <c r="AH5" s="1"/>
+      <c r="AH5" s="25"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
@@ -6060,7 +6064,7 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="1"/>
+      <c r="AH6" s="25"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -6177,7 +6181,7 @@
         <f t="shared" ref="AG7:AG70" si="7">G7*R7</f>
         <v>72</v>
       </c>
-      <c r="AH7" s="1"/>
+      <c r="AH7" s="25"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -6245,7 +6249,7 @@
         <v>7.5319999999999965</v>
       </c>
       <c r="R8" s="5">
-        <f t="shared" ref="R7:R70" si="8">ROUND(Q8,0)</f>
+        <f t="shared" ref="R8:R67" si="8">ROUND(Q8,0)</f>
         <v>8</v>
       </c>
       <c r="S8" s="23"/>
@@ -6292,7 +6296,7 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="AH8" s="1"/>
+      <c r="AH8" s="25"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
@@ -6409,7 +6413,7 @@
         <f t="shared" si="7"/>
         <v>52.5</v>
       </c>
-      <c r="AH9" s="1"/>
+      <c r="AH9" s="25"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
@@ -6526,7 +6530,7 @@
         <f t="shared" si="7"/>
         <v>240</v>
       </c>
-      <c r="AH10" s="1"/>
+      <c r="AH10" s="25"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
@@ -6643,7 +6647,7 @@
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AH11" s="1"/>
+      <c r="AH11" s="25"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
@@ -6760,7 +6764,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="1"/>
+      <c r="AH12" s="25"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
@@ -6877,7 +6881,7 @@
         <f t="shared" si="7"/>
         <v>140</v>
       </c>
-      <c r="AH13" s="1"/>
+      <c r="AH13" s="25"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
@@ -6991,7 +6995,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AH14" s="1"/>
+      <c r="AH14" s="25"/>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
@@ -7108,7 +7112,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="1"/>
+      <c r="AH15" s="25"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
@@ -7223,7 +7227,7 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="AH16" s="1"/>
+      <c r="AH16" s="25"/>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
@@ -7338,7 +7342,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="1"/>
+      <c r="AH17" s="25"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
@@ -7455,7 +7459,7 @@
         <f t="shared" si="7"/>
         <v>160</v>
       </c>
-      <c r="AH18" s="1"/>
+      <c r="AH18" s="25"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
@@ -7572,7 +7576,7 @@
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AH19" s="1"/>
+      <c r="AH19" s="25"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
@@ -7686,7 +7690,7 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AH20" s="1"/>
+      <c r="AH20" s="25"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
@@ -7803,7 +7807,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="1"/>
+      <c r="AH21" s="25"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
@@ -7920,7 +7924,7 @@
         <f t="shared" si="7"/>
         <v>66</v>
       </c>
-      <c r="AH22" s="1"/>
+      <c r="AH22" s="25"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
@@ -8037,7 +8041,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="AH23" s="1"/>
+      <c r="AH23" s="25"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
@@ -8151,7 +8155,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="AH24" s="1"/>
+      <c r="AH24" s="25"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
@@ -8268,7 +8272,7 @@
         <f t="shared" si="7"/>
         <v>5.3999999999999995</v>
       </c>
-      <c r="AH25" s="1"/>
+      <c r="AH25" s="25"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
@@ -8385,7 +8389,7 @@
         <f t="shared" si="7"/>
         <v>3.15</v>
       </c>
-      <c r="AH26" s="1"/>
+      <c r="AH26" s="25"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
@@ -8504,7 +8508,7 @@
         <f t="shared" si="7"/>
         <v>9.75</v>
       </c>
-      <c r="AH27" s="1"/>
+      <c r="AH27" s="25"/>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
@@ -8621,7 +8625,7 @@
         <f t="shared" si="7"/>
         <v>770</v>
       </c>
-      <c r="AH28" s="1"/>
+      <c r="AH28" s="25"/>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
@@ -8735,7 +8739,7 @@
         <f t="shared" si="7"/>
         <v>6.4</v>
       </c>
-      <c r="AH29" s="1"/>
+      <c r="AH29" s="25"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
@@ -8852,7 +8856,7 @@
         <f t="shared" si="7"/>
         <v>124</v>
       </c>
-      <c r="AH30" s="1"/>
+      <c r="AH30" s="25"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
@@ -8969,7 +8973,7 @@
         <f t="shared" si="7"/>
         <v>152</v>
       </c>
-      <c r="AH31" s="1"/>
+      <c r="AH31" s="25"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
@@ -9084,7 +9088,7 @@
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="AH32" s="1"/>
+      <c r="AH32" s="25"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
@@ -9196,7 +9200,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="1"/>
+      <c r="AH33" s="25"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
@@ -9310,7 +9314,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="1"/>
+      <c r="AH34" s="25"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
@@ -9427,7 +9431,7 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AH35" s="1"/>
+      <c r="AH35" s="25"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
@@ -9542,7 +9546,7 @@
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
-      <c r="AH36" s="1"/>
+      <c r="AH36" s="25"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
@@ -9659,7 +9663,7 @@
         <f t="shared" si="7"/>
         <v>153</v>
       </c>
-      <c r="AH37" s="1"/>
+      <c r="AH37" s="25"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
@@ -9777,7 +9781,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AH38" s="1"/>
+      <c r="AH38" s="25"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
@@ -9892,7 +9896,7 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AH39" s="1"/>
+      <c r="AH39" s="25"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
@@ -10009,7 +10013,7 @@
         <f t="shared" si="7"/>
         <v>157.5</v>
       </c>
-      <c r="AH40" s="1"/>
+      <c r="AH40" s="25"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
@@ -10125,7 +10129,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="1"/>
+      <c r="AH41" s="25"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
@@ -10242,7 +10246,7 @@
         <f t="shared" si="7"/>
         <v>69.7</v>
       </c>
-      <c r="AH42" s="1"/>
+      <c r="AH42" s="25"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
@@ -10357,7 +10361,7 @@
         <f t="shared" si="7"/>
         <v>72</v>
       </c>
-      <c r="AH43" s="1"/>
+      <c r="AH43" s="25"/>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
@@ -10473,7 +10477,7 @@
         <f t="shared" si="7"/>
         <v>2.64</v>
       </c>
-      <c r="AH44" s="1"/>
+      <c r="AH44" s="25"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
@@ -10588,7 +10592,7 @@
         <f t="shared" si="7"/>
         <v>21.6</v>
       </c>
-      <c r="AH45" s="1"/>
+      <c r="AH45" s="25"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
@@ -10703,7 +10707,7 @@
         <f t="shared" si="7"/>
         <v>4.62</v>
       </c>
-      <c r="AH46" s="1"/>
+      <c r="AH46" s="25"/>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
@@ -10820,7 +10824,7 @@
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-      <c r="AH47" s="1"/>
+      <c r="AH47" s="25"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
@@ -10937,7 +10941,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH48" s="1"/>
+      <c r="AH48" s="25"/>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
@@ -11047,7 +11051,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="1"/>
+      <c r="AH49" s="25"/>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
@@ -11157,7 +11161,7 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AH50" s="1"/>
+      <c r="AH50" s="25"/>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
@@ -11273,7 +11277,7 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AH51" s="1"/>
+      <c r="AH51" s="25"/>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
@@ -11385,7 +11389,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="1"/>
+      <c r="AH52" s="25"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
@@ -11502,7 +11506,7 @@
         <f t="shared" si="7"/>
         <v>190</v>
       </c>
-      <c r="AH53" s="1"/>
+      <c r="AH53" s="25"/>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
@@ -11619,7 +11623,7 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="AH54" s="1"/>
+      <c r="AH54" s="25"/>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
@@ -11738,7 +11742,7 @@
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="AH55" s="1"/>
+      <c r="AH55" s="25"/>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
@@ -11856,7 +11860,7 @@
         <f t="shared" si="7"/>
         <v>274.7</v>
       </c>
-      <c r="AH56" s="1"/>
+      <c r="AH56" s="25"/>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
@@ -11971,7 +11975,7 @@
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="AH57" s="1"/>
+      <c r="AH57" s="25"/>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
@@ -12086,7 +12090,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH58" s="1"/>
+      <c r="AH58" s="25"/>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
@@ -12198,7 +12202,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="1"/>
+      <c r="AH59" s="25"/>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
@@ -12315,7 +12319,7 @@
         <f t="shared" si="7"/>
         <v>143.5</v>
       </c>
-      <c r="AH60" s="1"/>
+      <c r="AH60" s="25"/>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
@@ -12430,7 +12434,7 @@
         <f t="shared" si="7"/>
         <v>26</v>
       </c>
-      <c r="AH61" s="1"/>
+      <c r="AH61" s="25"/>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
@@ -12545,7 +12549,7 @@
         <f t="shared" si="7"/>
         <v>7.5</v>
       </c>
-      <c r="AH62" s="1"/>
+      <c r="AH62" s="25"/>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
@@ -12659,7 +12663,7 @@
         <f t="shared" si="7"/>
         <v>10.799999999999999</v>
       </c>
-      <c r="AH63" s="1"/>
+      <c r="AH63" s="25"/>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
@@ -12774,7 +12778,7 @@
         <f t="shared" si="7"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="AH64" s="1"/>
+      <c r="AH64" s="25"/>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
@@ -12886,7 +12890,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH65" s="1"/>
+      <c r="AH65" s="25"/>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
@@ -13003,7 +13007,7 @@
         <f t="shared" si="7"/>
         <v>175</v>
       </c>
-      <c r="AH66" s="1"/>
+      <c r="AH66" s="25"/>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
@@ -13105,7 +13109,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH67" s="1"/>
+      <c r="AH67" s="25"/>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
@@ -13222,7 +13226,7 @@
         <f t="shared" si="7"/>
         <v>180</v>
       </c>
-      <c r="AH68" s="1"/>
+      <c r="AH68" s="25"/>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
@@ -13339,7 +13343,7 @@
         <f t="shared" si="7"/>
         <v>170</v>
       </c>
-      <c r="AH69" s="1"/>
+      <c r="AH69" s="25"/>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
@@ -13456,7 +13460,7 @@
         <f t="shared" si="7"/>
         <v>157.5</v>
       </c>
-      <c r="AH70" s="1"/>
+      <c r="AH70" s="25"/>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
@@ -13573,7 +13577,7 @@
         <f t="shared" ref="AG71:AG107" si="18">G71*R71</f>
         <v>30</v>
       </c>
-      <c r="AH71" s="1"/>
+      <c r="AH71" s="25"/>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
@@ -13690,7 +13694,7 @@
         <f t="shared" si="18"/>
         <v>36</v>
       </c>
-      <c r="AH72" s="1"/>
+      <c r="AH72" s="25"/>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
@@ -13807,7 +13811,7 @@
         <f t="shared" si="18"/>
         <v>176.4</v>
       </c>
-      <c r="AH73" s="1"/>
+      <c r="AH73" s="25"/>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
@@ -13924,7 +13928,7 @@
         <f t="shared" si="18"/>
         <v>182.00000000000003</v>
       </c>
-      <c r="AH74" s="1"/>
+      <c r="AH74" s="25"/>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
@@ -14041,7 +14045,7 @@
         <f t="shared" si="18"/>
         <v>106.4</v>
       </c>
-      <c r="AH75" s="1"/>
+      <c r="AH75" s="25"/>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
@@ -14158,7 +14162,7 @@
         <f t="shared" si="18"/>
         <v>204</v>
       </c>
-      <c r="AH76" s="1"/>
+      <c r="AH76" s="25"/>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
@@ -14217,7 +14221,7 @@
       </c>
       <c r="Q77" s="5"/>
       <c r="R77" s="5">
-        <f t="shared" ref="R71:R107" si="19">ROUND(Q77,0)</f>
+        <f t="shared" ref="R77:R107" si="19">ROUND(Q77,0)</f>
         <v>0</v>
       </c>
       <c r="S77" s="23"/>
@@ -14266,7 +14270,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH77" s="1"/>
+      <c r="AH77" s="25"/>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
@@ -14380,7 +14384,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH78" s="1"/>
+      <c r="AH78" s="25"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
@@ -14494,7 +14498,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH79" s="1"/>
+      <c r="AH79" s="25"/>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
@@ -14609,7 +14613,10 @@
         <f t="shared" si="18"/>
         <v>24.84</v>
       </c>
-      <c r="AH80" s="1"/>
+      <c r="AH80" s="25">
+        <f>252/5/P80</f>
+        <v>1.9236641221374047</v>
+      </c>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
@@ -14723,7 +14730,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH81" s="1"/>
+      <c r="AH81" s="25"/>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
@@ -14837,7 +14844,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH82" s="1"/>
+      <c r="AH82" s="25"/>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
@@ -14954,7 +14961,7 @@
         <f t="shared" si="18"/>
         <v>5.28</v>
       </c>
-      <c r="AH83" s="1"/>
+      <c r="AH83" s="25"/>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
@@ -15068,7 +15075,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH84" s="1"/>
+      <c r="AH84" s="25"/>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
@@ -15185,7 +15192,7 @@
         <f t="shared" si="18"/>
         <v>122.99999999999999</v>
       </c>
-      <c r="AH85" s="1"/>
+      <c r="AH85" s="25"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
@@ -15299,7 +15306,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH86" s="1"/>
+      <c r="AH86" s="25"/>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
@@ -15413,7 +15420,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH87" s="1"/>
+      <c r="AH87" s="25"/>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
@@ -15525,7 +15532,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH88" s="1"/>
+      <c r="AH88" s="25"/>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
@@ -15637,7 +15644,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH89" s="1"/>
+      <c r="AH89" s="25"/>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
@@ -15748,7 +15755,7 @@
         <f t="shared" si="18"/>
         <v>15.600000000000001</v>
       </c>
-      <c r="AH90" s="1"/>
+      <c r="AH90" s="25"/>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
@@ -15861,7 +15868,7 @@
         <f t="shared" si="18"/>
         <v>8.75</v>
       </c>
-      <c r="AH91" s="1"/>
+      <c r="AH91" s="25"/>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
@@ -15970,7 +15977,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH92" s="1"/>
+      <c r="AH92" s="25"/>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
@@ -16083,7 +16090,7 @@
         <f t="shared" si="18"/>
         <v>24</v>
       </c>
-      <c r="AH93" s="1"/>
+      <c r="AH93" s="25"/>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
@@ -16196,7 +16203,10 @@
         <f t="shared" si="18"/>
         <v>51.81</v>
       </c>
-      <c r="AH94" s="1"/>
+      <c r="AH94" s="25">
+        <f>P94/V94</f>
+        <v>1.9411764705882355</v>
+      </c>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
@@ -16311,7 +16321,7 @@
         <f t="shared" si="18"/>
         <v>4.1000000000000005</v>
       </c>
-      <c r="AH95" s="1"/>
+      <c r="AH95" s="25"/>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
@@ -16428,7 +16438,10 @@
         <f t="shared" si="18"/>
         <v>2.6</v>
       </c>
-      <c r="AH96" s="1"/>
+      <c r="AH96" s="25">
+        <f>V96/W96</f>
+        <v>1.3148148148148147</v>
+      </c>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
@@ -16541,7 +16554,10 @@
         <f t="shared" si="18"/>
         <v>88</v>
       </c>
-      <c r="AH97" s="1"/>
+      <c r="AH97" s="25">
+        <f>P97/V97</f>
+        <v>3.0540540540540539</v>
+      </c>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
@@ -16649,7 +16665,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH98" s="1"/>
+      <c r="AH98" s="25"/>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
@@ -16759,7 +16775,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH99" s="1"/>
+      <c r="AH99" s="25"/>
       <c r="AI99" s="1"/>
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
@@ -16871,7 +16887,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH100" s="1"/>
+      <c r="AH100" s="25"/>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
@@ -16981,7 +16997,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH101" s="1"/>
+      <c r="AH101" s="25"/>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
@@ -17091,7 +17107,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH102" s="1"/>
+      <c r="AH102" s="25"/>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
@@ -17195,7 +17211,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH103" s="1"/>
+      <c r="AH103" s="25"/>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
@@ -17301,7 +17317,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH104" s="1"/>
+      <c r="AH104" s="25"/>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
@@ -17401,7 +17417,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH105" s="1"/>
+      <c r="AH105" s="25"/>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
@@ -17501,7 +17517,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH106" s="1"/>
+      <c r="AH106" s="25"/>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
@@ -17601,7 +17617,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AH107" s="1"/>
+      <c r="AH107" s="25"/>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
@@ -17653,7 +17669,7 @@
       <c r="AE108" s="1"/>
       <c r="AF108" s="1"/>
       <c r="AG108" s="1"/>
-      <c r="AH108" s="1"/>
+      <c r="AH108" s="25"/>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
@@ -17705,7 +17721,7 @@
       <c r="AE109" s="1"/>
       <c r="AF109" s="1"/>
       <c r="AG109" s="1"/>
-      <c r="AH109" s="1"/>
+      <c r="AH109" s="25"/>
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
@@ -17757,7 +17773,7 @@
       <c r="AE110" s="1"/>
       <c r="AF110" s="1"/>
       <c r="AG110" s="1"/>
-      <c r="AH110" s="1"/>
+      <c r="AH110" s="25"/>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
@@ -17809,7 +17825,7 @@
       <c r="AE111" s="1"/>
       <c r="AF111" s="1"/>
       <c r="AG111" s="1"/>
-      <c r="AH111" s="1"/>
+      <c r="AH111" s="25"/>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
@@ -17861,7 +17877,7 @@
       <c r="AE112" s="1"/>
       <c r="AF112" s="1"/>
       <c r="AG112" s="1"/>
-      <c r="AH112" s="1"/>
+      <c r="AH112" s="25"/>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
@@ -17913,7 +17929,7 @@
       <c r="AE113" s="1"/>
       <c r="AF113" s="1"/>
       <c r="AG113" s="1"/>
-      <c r="AH113" s="1"/>
+      <c r="AH113" s="25"/>
       <c r="AI113" s="1"/>
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
@@ -17965,7 +17981,7 @@
       <c r="AE114" s="1"/>
       <c r="AF114" s="1"/>
       <c r="AG114" s="1"/>
-      <c r="AH114" s="1"/>
+      <c r="AH114" s="25"/>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
@@ -18017,7 +18033,7 @@
       <c r="AE115" s="1"/>
       <c r="AF115" s="1"/>
       <c r="AG115" s="1"/>
-      <c r="AH115" s="1"/>
+      <c r="AH115" s="25"/>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
@@ -18069,7 +18085,7 @@
       <c r="AE116" s="1"/>
       <c r="AF116" s="1"/>
       <c r="AG116" s="1"/>
-      <c r="AH116" s="1"/>
+      <c r="AH116" s="25"/>
       <c r="AI116" s="1"/>
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
@@ -18121,7 +18137,7 @@
       <c r="AE117" s="1"/>
       <c r="AF117" s="1"/>
       <c r="AG117" s="1"/>
-      <c r="AH117" s="1"/>
+      <c r="AH117" s="25"/>
       <c r="AI117" s="1"/>
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
@@ -18173,7 +18189,7 @@
       <c r="AE118" s="1"/>
       <c r="AF118" s="1"/>
       <c r="AG118" s="1"/>
-      <c r="AH118" s="1"/>
+      <c r="AH118" s="25"/>
       <c r="AI118" s="1"/>
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
@@ -18225,7 +18241,7 @@
       <c r="AE119" s="1"/>
       <c r="AF119" s="1"/>
       <c r="AG119" s="1"/>
-      <c r="AH119" s="1"/>
+      <c r="AH119" s="25"/>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
@@ -18277,7 +18293,7 @@
       <c r="AE120" s="1"/>
       <c r="AF120" s="1"/>
       <c r="AG120" s="1"/>
-      <c r="AH120" s="1"/>
+      <c r="AH120" s="25"/>
       <c r="AI120" s="1"/>
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
@@ -18329,7 +18345,7 @@
       <c r="AE121" s="1"/>
       <c r="AF121" s="1"/>
       <c r="AG121" s="1"/>
-      <c r="AH121" s="1"/>
+      <c r="AH121" s="25"/>
       <c r="AI121" s="1"/>
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
@@ -18381,7 +18397,7 @@
       <c r="AE122" s="1"/>
       <c r="AF122" s="1"/>
       <c r="AG122" s="1"/>
-      <c r="AH122" s="1"/>
+      <c r="AH122" s="25"/>
       <c r="AI122" s="1"/>
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
@@ -18433,7 +18449,7 @@
       <c r="AE123" s="1"/>
       <c r="AF123" s="1"/>
       <c r="AG123" s="1"/>
-      <c r="AH123" s="1"/>
+      <c r="AH123" s="25"/>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
@@ -18485,7 +18501,7 @@
       <c r="AE124" s="1"/>
       <c r="AF124" s="1"/>
       <c r="AG124" s="1"/>
-      <c r="AH124" s="1"/>
+      <c r="AH124" s="25"/>
       <c r="AI124" s="1"/>
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
@@ -18537,7 +18553,7 @@
       <c r="AE125" s="1"/>
       <c r="AF125" s="1"/>
       <c r="AG125" s="1"/>
-      <c r="AH125" s="1"/>
+      <c r="AH125" s="25"/>
       <c r="AI125" s="1"/>
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
@@ -18589,7 +18605,7 @@
       <c r="AE126" s="1"/>
       <c r="AF126" s="1"/>
       <c r="AG126" s="1"/>
-      <c r="AH126" s="1"/>
+      <c r="AH126" s="25"/>
       <c r="AI126" s="1"/>
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
@@ -18641,7 +18657,7 @@
       <c r="AE127" s="1"/>
       <c r="AF127" s="1"/>
       <c r="AG127" s="1"/>
-      <c r="AH127" s="1"/>
+      <c r="AH127" s="25"/>
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
@@ -18693,7 +18709,7 @@
       <c r="AE128" s="1"/>
       <c r="AF128" s="1"/>
       <c r="AG128" s="1"/>
-      <c r="AH128" s="1"/>
+      <c r="AH128" s="25"/>
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
@@ -18745,7 +18761,7 @@
       <c r="AE129" s="1"/>
       <c r="AF129" s="1"/>
       <c r="AG129" s="1"/>
-      <c r="AH129" s="1"/>
+      <c r="AH129" s="25"/>
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
@@ -18797,7 +18813,7 @@
       <c r="AE130" s="1"/>
       <c r="AF130" s="1"/>
       <c r="AG130" s="1"/>
-      <c r="AH130" s="1"/>
+      <c r="AH130" s="25"/>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
@@ -18849,7 +18865,7 @@
       <c r="AE131" s="1"/>
       <c r="AF131" s="1"/>
       <c r="AG131" s="1"/>
-      <c r="AH131" s="1"/>
+      <c r="AH131" s="25"/>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
@@ -18901,7 +18917,7 @@
       <c r="AE132" s="1"/>
       <c r="AF132" s="1"/>
       <c r="AG132" s="1"/>
-      <c r="AH132" s="1"/>
+      <c r="AH132" s="25"/>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
@@ -18953,7 +18969,7 @@
       <c r="AE133" s="1"/>
       <c r="AF133" s="1"/>
       <c r="AG133" s="1"/>
-      <c r="AH133" s="1"/>
+      <c r="AH133" s="25"/>
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
@@ -19005,7 +19021,7 @@
       <c r="AE134" s="1"/>
       <c r="AF134" s="1"/>
       <c r="AG134" s="1"/>
-      <c r="AH134" s="1"/>
+      <c r="AH134" s="25"/>
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
@@ -19057,7 +19073,7 @@
       <c r="AE135" s="1"/>
       <c r="AF135" s="1"/>
       <c r="AG135" s="1"/>
-      <c r="AH135" s="1"/>
+      <c r="AH135" s="25"/>
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
@@ -19109,7 +19125,7 @@
       <c r="AE136" s="1"/>
       <c r="AF136" s="1"/>
       <c r="AG136" s="1"/>
-      <c r="AH136" s="1"/>
+      <c r="AH136" s="25"/>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
@@ -19161,7 +19177,7 @@
       <c r="AE137" s="1"/>
       <c r="AF137" s="1"/>
       <c r="AG137" s="1"/>
-      <c r="AH137" s="1"/>
+      <c r="AH137" s="25"/>
       <c r="AI137" s="1"/>
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
@@ -19213,7 +19229,7 @@
       <c r="AE138" s="1"/>
       <c r="AF138" s="1"/>
       <c r="AG138" s="1"/>
-      <c r="AH138" s="1"/>
+      <c r="AH138" s="25"/>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
@@ -19265,7 +19281,7 @@
       <c r="AE139" s="1"/>
       <c r="AF139" s="1"/>
       <c r="AG139" s="1"/>
-      <c r="AH139" s="1"/>
+      <c r="AH139" s="25"/>
       <c r="AI139" s="1"/>
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
@@ -19317,7 +19333,7 @@
       <c r="AE140" s="1"/>
       <c r="AF140" s="1"/>
       <c r="AG140" s="1"/>
-      <c r="AH140" s="1"/>
+      <c r="AH140" s="25"/>
       <c r="AI140" s="1"/>
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
@@ -19369,7 +19385,7 @@
       <c r="AE141" s="1"/>
       <c r="AF141" s="1"/>
       <c r="AG141" s="1"/>
-      <c r="AH141" s="1"/>
+      <c r="AH141" s="25"/>
       <c r="AI141" s="1"/>
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
@@ -19421,7 +19437,7 @@
       <c r="AE142" s="1"/>
       <c r="AF142" s="1"/>
       <c r="AG142" s="1"/>
-      <c r="AH142" s="1"/>
+      <c r="AH142" s="25"/>
       <c r="AI142" s="1"/>
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
@@ -19473,7 +19489,7 @@
       <c r="AE143" s="1"/>
       <c r="AF143" s="1"/>
       <c r="AG143" s="1"/>
-      <c r="AH143" s="1"/>
+      <c r="AH143" s="25"/>
       <c r="AI143" s="1"/>
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
@@ -19525,7 +19541,7 @@
       <c r="AE144" s="1"/>
       <c r="AF144" s="1"/>
       <c r="AG144" s="1"/>
-      <c r="AH144" s="1"/>
+      <c r="AH144" s="25"/>
       <c r="AI144" s="1"/>
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
@@ -19577,7 +19593,7 @@
       <c r="AE145" s="1"/>
       <c r="AF145" s="1"/>
       <c r="AG145" s="1"/>
-      <c r="AH145" s="1"/>
+      <c r="AH145" s="25"/>
       <c r="AI145" s="1"/>
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
@@ -19629,7 +19645,7 @@
       <c r="AE146" s="1"/>
       <c r="AF146" s="1"/>
       <c r="AG146" s="1"/>
-      <c r="AH146" s="1"/>
+      <c r="AH146" s="25"/>
       <c r="AI146" s="1"/>
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
@@ -19681,7 +19697,7 @@
       <c r="AE147" s="1"/>
       <c r="AF147" s="1"/>
       <c r="AG147" s="1"/>
-      <c r="AH147" s="1"/>
+      <c r="AH147" s="25"/>
       <c r="AI147" s="1"/>
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
@@ -19733,7 +19749,7 @@
       <c r="AE148" s="1"/>
       <c r="AF148" s="1"/>
       <c r="AG148" s="1"/>
-      <c r="AH148" s="1"/>
+      <c r="AH148" s="25"/>
       <c r="AI148" s="1"/>
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
@@ -19785,7 +19801,7 @@
       <c r="AE149" s="1"/>
       <c r="AF149" s="1"/>
       <c r="AG149" s="1"/>
-      <c r="AH149" s="1"/>
+      <c r="AH149" s="25"/>
       <c r="AI149" s="1"/>
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
@@ -19837,7 +19853,7 @@
       <c r="AE150" s="1"/>
       <c r="AF150" s="1"/>
       <c r="AG150" s="1"/>
-      <c r="AH150" s="1"/>
+      <c r="AH150" s="25"/>
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
@@ -19889,7 +19905,7 @@
       <c r="AE151" s="1"/>
       <c r="AF151" s="1"/>
       <c r="AG151" s="1"/>
-      <c r="AH151" s="1"/>
+      <c r="AH151" s="25"/>
       <c r="AI151" s="1"/>
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
@@ -19941,7 +19957,7 @@
       <c r="AE152" s="1"/>
       <c r="AF152" s="1"/>
       <c r="AG152" s="1"/>
-      <c r="AH152" s="1"/>
+      <c r="AH152" s="25"/>
       <c r="AI152" s="1"/>
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
@@ -19993,7 +20009,7 @@
       <c r="AE153" s="1"/>
       <c r="AF153" s="1"/>
       <c r="AG153" s="1"/>
-      <c r="AH153" s="1"/>
+      <c r="AH153" s="25"/>
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
@@ -20045,7 +20061,7 @@
       <c r="AE154" s="1"/>
       <c r="AF154" s="1"/>
       <c r="AG154" s="1"/>
-      <c r="AH154" s="1"/>
+      <c r="AH154" s="25"/>
       <c r="AI154" s="1"/>
       <c r="AJ154" s="1"/>
       <c r="AK154" s="1"/>
@@ -20097,7 +20113,7 @@
       <c r="AE155" s="1"/>
       <c r="AF155" s="1"/>
       <c r="AG155" s="1"/>
-      <c r="AH155" s="1"/>
+      <c r="AH155" s="25"/>
       <c r="AI155" s="1"/>
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
@@ -20149,7 +20165,7 @@
       <c r="AE156" s="1"/>
       <c r="AF156" s="1"/>
       <c r="AG156" s="1"/>
-      <c r="AH156" s="1"/>
+      <c r="AH156" s="25"/>
       <c r="AI156" s="1"/>
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
@@ -20201,7 +20217,7 @@
       <c r="AE157" s="1"/>
       <c r="AF157" s="1"/>
       <c r="AG157" s="1"/>
-      <c r="AH157" s="1"/>
+      <c r="AH157" s="25"/>
       <c r="AI157" s="1"/>
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
@@ -20253,7 +20269,7 @@
       <c r="AE158" s="1"/>
       <c r="AF158" s="1"/>
       <c r="AG158" s="1"/>
-      <c r="AH158" s="1"/>
+      <c r="AH158" s="25"/>
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
@@ -20305,7 +20321,7 @@
       <c r="AE159" s="1"/>
       <c r="AF159" s="1"/>
       <c r="AG159" s="1"/>
-      <c r="AH159" s="1"/>
+      <c r="AH159" s="25"/>
       <c r="AI159" s="1"/>
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
@@ -20357,7 +20373,7 @@
       <c r="AE160" s="1"/>
       <c r="AF160" s="1"/>
       <c r="AG160" s="1"/>
-      <c r="AH160" s="1"/>
+      <c r="AH160" s="25"/>
       <c r="AI160" s="1"/>
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
@@ -20409,7 +20425,7 @@
       <c r="AE161" s="1"/>
       <c r="AF161" s="1"/>
       <c r="AG161" s="1"/>
-      <c r="AH161" s="1"/>
+      <c r="AH161" s="25"/>
       <c r="AI161" s="1"/>
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
@@ -20461,7 +20477,7 @@
       <c r="AE162" s="1"/>
       <c r="AF162" s="1"/>
       <c r="AG162" s="1"/>
-      <c r="AH162" s="1"/>
+      <c r="AH162" s="25"/>
       <c r="AI162" s="1"/>
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
@@ -20513,7 +20529,7 @@
       <c r="AE163" s="1"/>
       <c r="AF163" s="1"/>
       <c r="AG163" s="1"/>
-      <c r="AH163" s="1"/>
+      <c r="AH163" s="25"/>
       <c r="AI163" s="1"/>
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
@@ -20565,7 +20581,7 @@
       <c r="AE164" s="1"/>
       <c r="AF164" s="1"/>
       <c r="AG164" s="1"/>
-      <c r="AH164" s="1"/>
+      <c r="AH164" s="25"/>
       <c r="AI164" s="1"/>
       <c r="AJ164" s="1"/>
       <c r="AK164" s="1"/>
@@ -20617,7 +20633,7 @@
       <c r="AE165" s="1"/>
       <c r="AF165" s="1"/>
       <c r="AG165" s="1"/>
-      <c r="AH165" s="1"/>
+      <c r="AH165" s="25"/>
       <c r="AI165" s="1"/>
       <c r="AJ165" s="1"/>
       <c r="AK165" s="1"/>
@@ -20669,7 +20685,7 @@
       <c r="AE166" s="1"/>
       <c r="AF166" s="1"/>
       <c r="AG166" s="1"/>
-      <c r="AH166" s="1"/>
+      <c r="AH166" s="25"/>
       <c r="AI166" s="1"/>
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
@@ -20721,7 +20737,7 @@
       <c r="AE167" s="1"/>
       <c r="AF167" s="1"/>
       <c r="AG167" s="1"/>
-      <c r="AH167" s="1"/>
+      <c r="AH167" s="25"/>
       <c r="AI167" s="1"/>
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
@@ -20773,7 +20789,7 @@
       <c r="AE168" s="1"/>
       <c r="AF168" s="1"/>
       <c r="AG168" s="1"/>
-      <c r="AH168" s="1"/>
+      <c r="AH168" s="25"/>
       <c r="AI168" s="1"/>
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
@@ -20825,7 +20841,7 @@
       <c r="AE169" s="1"/>
       <c r="AF169" s="1"/>
       <c r="AG169" s="1"/>
-      <c r="AH169" s="1"/>
+      <c r="AH169" s="25"/>
       <c r="AI169" s="1"/>
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
@@ -20877,7 +20893,7 @@
       <c r="AE170" s="1"/>
       <c r="AF170" s="1"/>
       <c r="AG170" s="1"/>
-      <c r="AH170" s="1"/>
+      <c r="AH170" s="25"/>
       <c r="AI170" s="1"/>
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
@@ -20929,7 +20945,7 @@
       <c r="AE171" s="1"/>
       <c r="AF171" s="1"/>
       <c r="AG171" s="1"/>
-      <c r="AH171" s="1"/>
+      <c r="AH171" s="25"/>
       <c r="AI171" s="1"/>
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
@@ -20981,7 +20997,7 @@
       <c r="AE172" s="1"/>
       <c r="AF172" s="1"/>
       <c r="AG172" s="1"/>
-      <c r="AH172" s="1"/>
+      <c r="AH172" s="25"/>
       <c r="AI172" s="1"/>
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
@@ -21033,7 +21049,7 @@
       <c r="AE173" s="1"/>
       <c r="AF173" s="1"/>
       <c r="AG173" s="1"/>
-      <c r="AH173" s="1"/>
+      <c r="AH173" s="25"/>
       <c r="AI173" s="1"/>
       <c r="AJ173" s="1"/>
       <c r="AK173" s="1"/>
@@ -21085,7 +21101,7 @@
       <c r="AE174" s="1"/>
       <c r="AF174" s="1"/>
       <c r="AG174" s="1"/>
-      <c r="AH174" s="1"/>
+      <c r="AH174" s="25"/>
       <c r="AI174" s="1"/>
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
@@ -21137,7 +21153,7 @@
       <c r="AE175" s="1"/>
       <c r="AF175" s="1"/>
       <c r="AG175" s="1"/>
-      <c r="AH175" s="1"/>
+      <c r="AH175" s="25"/>
       <c r="AI175" s="1"/>
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
@@ -21189,7 +21205,7 @@
       <c r="AE176" s="1"/>
       <c r="AF176" s="1"/>
       <c r="AG176" s="1"/>
-      <c r="AH176" s="1"/>
+      <c r="AH176" s="25"/>
       <c r="AI176" s="1"/>
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
@@ -21241,7 +21257,7 @@
       <c r="AE177" s="1"/>
       <c r="AF177" s="1"/>
       <c r="AG177" s="1"/>
-      <c r="AH177" s="1"/>
+      <c r="AH177" s="25"/>
       <c r="AI177" s="1"/>
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
@@ -21293,7 +21309,7 @@
       <c r="AE178" s="1"/>
       <c r="AF178" s="1"/>
       <c r="AG178" s="1"/>
-      <c r="AH178" s="1"/>
+      <c r="AH178" s="25"/>
       <c r="AI178" s="1"/>
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
@@ -21345,7 +21361,7 @@
       <c r="AE179" s="1"/>
       <c r="AF179" s="1"/>
       <c r="AG179" s="1"/>
-      <c r="AH179" s="1"/>
+      <c r="AH179" s="25"/>
       <c r="AI179" s="1"/>
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
@@ -21397,7 +21413,7 @@
       <c r="AE180" s="1"/>
       <c r="AF180" s="1"/>
       <c r="AG180" s="1"/>
-      <c r="AH180" s="1"/>
+      <c r="AH180" s="25"/>
       <c r="AI180" s="1"/>
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
@@ -21449,7 +21465,7 @@
       <c r="AE181" s="1"/>
       <c r="AF181" s="1"/>
       <c r="AG181" s="1"/>
-      <c r="AH181" s="1"/>
+      <c r="AH181" s="25"/>
       <c r="AI181" s="1"/>
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
@@ -21501,7 +21517,7 @@
       <c r="AE182" s="1"/>
       <c r="AF182" s="1"/>
       <c r="AG182" s="1"/>
-      <c r="AH182" s="1"/>
+      <c r="AH182" s="25"/>
       <c r="AI182" s="1"/>
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
@@ -21553,7 +21569,7 @@
       <c r="AE183" s="1"/>
       <c r="AF183" s="1"/>
       <c r="AG183" s="1"/>
-      <c r="AH183" s="1"/>
+      <c r="AH183" s="25"/>
       <c r="AI183" s="1"/>
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
@@ -21605,7 +21621,7 @@
       <c r="AE184" s="1"/>
       <c r="AF184" s="1"/>
       <c r="AG184" s="1"/>
-      <c r="AH184" s="1"/>
+      <c r="AH184" s="25"/>
       <c r="AI184" s="1"/>
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
@@ -21657,7 +21673,7 @@
       <c r="AE185" s="1"/>
       <c r="AF185" s="1"/>
       <c r="AG185" s="1"/>
-      <c r="AH185" s="1"/>
+      <c r="AH185" s="25"/>
       <c r="AI185" s="1"/>
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
@@ -21709,7 +21725,7 @@
       <c r="AE186" s="1"/>
       <c r="AF186" s="1"/>
       <c r="AG186" s="1"/>
-      <c r="AH186" s="1"/>
+      <c r="AH186" s="25"/>
       <c r="AI186" s="1"/>
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
@@ -21761,7 +21777,7 @@
       <c r="AE187" s="1"/>
       <c r="AF187" s="1"/>
       <c r="AG187" s="1"/>
-      <c r="AH187" s="1"/>
+      <c r="AH187" s="25"/>
       <c r="AI187" s="1"/>
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
@@ -21813,7 +21829,7 @@
       <c r="AE188" s="1"/>
       <c r="AF188" s="1"/>
       <c r="AG188" s="1"/>
-      <c r="AH188" s="1"/>
+      <c r="AH188" s="25"/>
       <c r="AI188" s="1"/>
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
@@ -21865,7 +21881,7 @@
       <c r="AE189" s="1"/>
       <c r="AF189" s="1"/>
       <c r="AG189" s="1"/>
-      <c r="AH189" s="1"/>
+      <c r="AH189" s="25"/>
       <c r="AI189" s="1"/>
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
@@ -21917,7 +21933,7 @@
       <c r="AE190" s="1"/>
       <c r="AF190" s="1"/>
       <c r="AG190" s="1"/>
-      <c r="AH190" s="1"/>
+      <c r="AH190" s="25"/>
       <c r="AI190" s="1"/>
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
@@ -21969,7 +21985,7 @@
       <c r="AE191" s="1"/>
       <c r="AF191" s="1"/>
       <c r="AG191" s="1"/>
-      <c r="AH191" s="1"/>
+      <c r="AH191" s="25"/>
       <c r="AI191" s="1"/>
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
@@ -22021,7 +22037,7 @@
       <c r="AE192" s="1"/>
       <c r="AF192" s="1"/>
       <c r="AG192" s="1"/>
-      <c r="AH192" s="1"/>
+      <c r="AH192" s="25"/>
       <c r="AI192" s="1"/>
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
@@ -22073,7 +22089,7 @@
       <c r="AE193" s="1"/>
       <c r="AF193" s="1"/>
       <c r="AG193" s="1"/>
-      <c r="AH193" s="1"/>
+      <c r="AH193" s="25"/>
       <c r="AI193" s="1"/>
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
@@ -22125,7 +22141,7 @@
       <c r="AE194" s="1"/>
       <c r="AF194" s="1"/>
       <c r="AG194" s="1"/>
-      <c r="AH194" s="1"/>
+      <c r="AH194" s="25"/>
       <c r="AI194" s="1"/>
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
@@ -22177,7 +22193,7 @@
       <c r="AE195" s="1"/>
       <c r="AF195" s="1"/>
       <c r="AG195" s="1"/>
-      <c r="AH195" s="1"/>
+      <c r="AH195" s="25"/>
       <c r="AI195" s="1"/>
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
@@ -22229,7 +22245,7 @@
       <c r="AE196" s="1"/>
       <c r="AF196" s="1"/>
       <c r="AG196" s="1"/>
-      <c r="AH196" s="1"/>
+      <c r="AH196" s="25"/>
       <c r="AI196" s="1"/>
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
@@ -22281,7 +22297,7 @@
       <c r="AE197" s="1"/>
       <c r="AF197" s="1"/>
       <c r="AG197" s="1"/>
-      <c r="AH197" s="1"/>
+      <c r="AH197" s="25"/>
       <c r="AI197" s="1"/>
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
@@ -22333,7 +22349,7 @@
       <c r="AE198" s="1"/>
       <c r="AF198" s="1"/>
       <c r="AG198" s="1"/>
-      <c r="AH198" s="1"/>
+      <c r="AH198" s="25"/>
       <c r="AI198" s="1"/>
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
@@ -22385,7 +22401,7 @@
       <c r="AE199" s="1"/>
       <c r="AF199" s="1"/>
       <c r="AG199" s="1"/>
-      <c r="AH199" s="1"/>
+      <c r="AH199" s="25"/>
       <c r="AI199" s="1"/>
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
@@ -22437,7 +22453,7 @@
       <c r="AE200" s="1"/>
       <c r="AF200" s="1"/>
       <c r="AG200" s="1"/>
-      <c r="AH200" s="1"/>
+      <c r="AH200" s="25"/>
       <c r="AI200" s="1"/>
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
@@ -22489,7 +22505,7 @@
       <c r="AE201" s="1"/>
       <c r="AF201" s="1"/>
       <c r="AG201" s="1"/>
-      <c r="AH201" s="1"/>
+      <c r="AH201" s="25"/>
       <c r="AI201" s="1"/>
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
@@ -22541,7 +22557,7 @@
       <c r="AE202" s="1"/>
       <c r="AF202" s="1"/>
       <c r="AG202" s="1"/>
-      <c r="AH202" s="1"/>
+      <c r="AH202" s="25"/>
       <c r="AI202" s="1"/>
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
@@ -22593,7 +22609,7 @@
       <c r="AE203" s="1"/>
       <c r="AF203" s="1"/>
       <c r="AG203" s="1"/>
-      <c r="AH203" s="1"/>
+      <c r="AH203" s="25"/>
       <c r="AI203" s="1"/>
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
@@ -22645,7 +22661,7 @@
       <c r="AE204" s="1"/>
       <c r="AF204" s="1"/>
       <c r="AG204" s="1"/>
-      <c r="AH204" s="1"/>
+      <c r="AH204" s="25"/>
       <c r="AI204" s="1"/>
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
@@ -22697,7 +22713,7 @@
       <c r="AE205" s="1"/>
       <c r="AF205" s="1"/>
       <c r="AG205" s="1"/>
-      <c r="AH205" s="1"/>
+      <c r="AH205" s="25"/>
       <c r="AI205" s="1"/>
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
@@ -22749,7 +22765,7 @@
       <c r="AE206" s="1"/>
       <c r="AF206" s="1"/>
       <c r="AG206" s="1"/>
-      <c r="AH206" s="1"/>
+      <c r="AH206" s="25"/>
       <c r="AI206" s="1"/>
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
@@ -22801,7 +22817,7 @@
       <c r="AE207" s="1"/>
       <c r="AF207" s="1"/>
       <c r="AG207" s="1"/>
-      <c r="AH207" s="1"/>
+      <c r="AH207" s="25"/>
       <c r="AI207" s="1"/>
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
@@ -22853,7 +22869,7 @@
       <c r="AE208" s="1"/>
       <c r="AF208" s="1"/>
       <c r="AG208" s="1"/>
-      <c r="AH208" s="1"/>
+      <c r="AH208" s="25"/>
       <c r="AI208" s="1"/>
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
@@ -22905,7 +22921,7 @@
       <c r="AE209" s="1"/>
       <c r="AF209" s="1"/>
       <c r="AG209" s="1"/>
-      <c r="AH209" s="1"/>
+      <c r="AH209" s="25"/>
       <c r="AI209" s="1"/>
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
@@ -22957,7 +22973,7 @@
       <c r="AE210" s="1"/>
       <c r="AF210" s="1"/>
       <c r="AG210" s="1"/>
-      <c r="AH210" s="1"/>
+      <c r="AH210" s="25"/>
       <c r="AI210" s="1"/>
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
@@ -23009,7 +23025,7 @@
       <c r="AE211" s="1"/>
       <c r="AF211" s="1"/>
       <c r="AG211" s="1"/>
-      <c r="AH211" s="1"/>
+      <c r="AH211" s="25"/>
       <c r="AI211" s="1"/>
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
@@ -23061,7 +23077,7 @@
       <c r="AE212" s="1"/>
       <c r="AF212" s="1"/>
       <c r="AG212" s="1"/>
-      <c r="AH212" s="1"/>
+      <c r="AH212" s="25"/>
       <c r="AI212" s="1"/>
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
@@ -23113,7 +23129,7 @@
       <c r="AE213" s="1"/>
       <c r="AF213" s="1"/>
       <c r="AG213" s="1"/>
-      <c r="AH213" s="1"/>
+      <c r="AH213" s="25"/>
       <c r="AI213" s="1"/>
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
@@ -23165,7 +23181,7 @@
       <c r="AE214" s="1"/>
       <c r="AF214" s="1"/>
       <c r="AG214" s="1"/>
-      <c r="AH214" s="1"/>
+      <c r="AH214" s="25"/>
       <c r="AI214" s="1"/>
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
@@ -23217,7 +23233,7 @@
       <c r="AE215" s="1"/>
       <c r="AF215" s="1"/>
       <c r="AG215" s="1"/>
-      <c r="AH215" s="1"/>
+      <c r="AH215" s="25"/>
       <c r="AI215" s="1"/>
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
@@ -23269,7 +23285,7 @@
       <c r="AE216" s="1"/>
       <c r="AF216" s="1"/>
       <c r="AG216" s="1"/>
-      <c r="AH216" s="1"/>
+      <c r="AH216" s="25"/>
       <c r="AI216" s="1"/>
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
@@ -23321,7 +23337,7 @@
       <c r="AE217" s="1"/>
       <c r="AF217" s="1"/>
       <c r="AG217" s="1"/>
-      <c r="AH217" s="1"/>
+      <c r="AH217" s="25"/>
       <c r="AI217" s="1"/>
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
@@ -23373,7 +23389,7 @@
       <c r="AE218" s="1"/>
       <c r="AF218" s="1"/>
       <c r="AG218" s="1"/>
-      <c r="AH218" s="1"/>
+      <c r="AH218" s="25"/>
       <c r="AI218" s="1"/>
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
@@ -23425,7 +23441,7 @@
       <c r="AE219" s="1"/>
       <c r="AF219" s="1"/>
       <c r="AG219" s="1"/>
-      <c r="AH219" s="1"/>
+      <c r="AH219" s="25"/>
       <c r="AI219" s="1"/>
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
@@ -23477,7 +23493,7 @@
       <c r="AE220" s="1"/>
       <c r="AF220" s="1"/>
       <c r="AG220" s="1"/>
-      <c r="AH220" s="1"/>
+      <c r="AH220" s="25"/>
       <c r="AI220" s="1"/>
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
@@ -23529,7 +23545,7 @@
       <c r="AE221" s="1"/>
       <c r="AF221" s="1"/>
       <c r="AG221" s="1"/>
-      <c r="AH221" s="1"/>
+      <c r="AH221" s="25"/>
       <c r="AI221" s="1"/>
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
@@ -23581,7 +23597,7 @@
       <c r="AE222" s="1"/>
       <c r="AF222" s="1"/>
       <c r="AG222" s="1"/>
-      <c r="AH222" s="1"/>
+      <c r="AH222" s="25"/>
       <c r="AI222" s="1"/>
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
@@ -23633,7 +23649,7 @@
       <c r="AE223" s="1"/>
       <c r="AF223" s="1"/>
       <c r="AG223" s="1"/>
-      <c r="AH223" s="1"/>
+      <c r="AH223" s="25"/>
       <c r="AI223" s="1"/>
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
@@ -23685,7 +23701,7 @@
       <c r="AE224" s="1"/>
       <c r="AF224" s="1"/>
       <c r="AG224" s="1"/>
-      <c r="AH224" s="1"/>
+      <c r="AH224" s="25"/>
       <c r="AI224" s="1"/>
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
@@ -23737,7 +23753,7 @@
       <c r="AE225" s="1"/>
       <c r="AF225" s="1"/>
       <c r="AG225" s="1"/>
-      <c r="AH225" s="1"/>
+      <c r="AH225" s="25"/>
       <c r="AI225" s="1"/>
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
@@ -23789,7 +23805,7 @@
       <c r="AE226" s="1"/>
       <c r="AF226" s="1"/>
       <c r="AG226" s="1"/>
-      <c r="AH226" s="1"/>
+      <c r="AH226" s="25"/>
       <c r="AI226" s="1"/>
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
@@ -23841,7 +23857,7 @@
       <c r="AE227" s="1"/>
       <c r="AF227" s="1"/>
       <c r="AG227" s="1"/>
-      <c r="AH227" s="1"/>
+      <c r="AH227" s="25"/>
       <c r="AI227" s="1"/>
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
@@ -23893,7 +23909,7 @@
       <c r="AE228" s="1"/>
       <c r="AF228" s="1"/>
       <c r="AG228" s="1"/>
-      <c r="AH228" s="1"/>
+      <c r="AH228" s="25"/>
       <c r="AI228" s="1"/>
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
@@ -23945,7 +23961,7 @@
       <c r="AE229" s="1"/>
       <c r="AF229" s="1"/>
       <c r="AG229" s="1"/>
-      <c r="AH229" s="1"/>
+      <c r="AH229" s="25"/>
       <c r="AI229" s="1"/>
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
@@ -23997,7 +24013,7 @@
       <c r="AE230" s="1"/>
       <c r="AF230" s="1"/>
       <c r="AG230" s="1"/>
-      <c r="AH230" s="1"/>
+      <c r="AH230" s="25"/>
       <c r="AI230" s="1"/>
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
@@ -24049,7 +24065,7 @@
       <c r="AE231" s="1"/>
       <c r="AF231" s="1"/>
       <c r="AG231" s="1"/>
-      <c r="AH231" s="1"/>
+      <c r="AH231" s="25"/>
       <c r="AI231" s="1"/>
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
@@ -24101,7 +24117,7 @@
       <c r="AE232" s="1"/>
       <c r="AF232" s="1"/>
       <c r="AG232" s="1"/>
-      <c r="AH232" s="1"/>
+      <c r="AH232" s="25"/>
       <c r="AI232" s="1"/>
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
@@ -24153,7 +24169,7 @@
       <c r="AE233" s="1"/>
       <c r="AF233" s="1"/>
       <c r="AG233" s="1"/>
-      <c r="AH233" s="1"/>
+      <c r="AH233" s="25"/>
       <c r="AI233" s="1"/>
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
@@ -24205,7 +24221,7 @@
       <c r="AE234" s="1"/>
       <c r="AF234" s="1"/>
       <c r="AG234" s="1"/>
-      <c r="AH234" s="1"/>
+      <c r="AH234" s="25"/>
       <c r="AI234" s="1"/>
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
@@ -24257,7 +24273,7 @@
       <c r="AE235" s="1"/>
       <c r="AF235" s="1"/>
       <c r="AG235" s="1"/>
-      <c r="AH235" s="1"/>
+      <c r="AH235" s="25"/>
       <c r="AI235" s="1"/>
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
@@ -24309,7 +24325,7 @@
       <c r="AE236" s="1"/>
       <c r="AF236" s="1"/>
       <c r="AG236" s="1"/>
-      <c r="AH236" s="1"/>
+      <c r="AH236" s="25"/>
       <c r="AI236" s="1"/>
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
@@ -24361,7 +24377,7 @@
       <c r="AE237" s="1"/>
       <c r="AF237" s="1"/>
       <c r="AG237" s="1"/>
-      <c r="AH237" s="1"/>
+      <c r="AH237" s="25"/>
       <c r="AI237" s="1"/>
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
@@ -24413,7 +24429,7 @@
       <c r="AE238" s="1"/>
       <c r="AF238" s="1"/>
       <c r="AG238" s="1"/>
-      <c r="AH238" s="1"/>
+      <c r="AH238" s="25"/>
       <c r="AI238" s="1"/>
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
@@ -24465,7 +24481,7 @@
       <c r="AE239" s="1"/>
       <c r="AF239" s="1"/>
       <c r="AG239" s="1"/>
-      <c r="AH239" s="1"/>
+      <c r="AH239" s="25"/>
       <c r="AI239" s="1"/>
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
@@ -24517,7 +24533,7 @@
       <c r="AE240" s="1"/>
       <c r="AF240" s="1"/>
       <c r="AG240" s="1"/>
-      <c r="AH240" s="1"/>
+      <c r="AH240" s="25"/>
       <c r="AI240" s="1"/>
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
@@ -24569,7 +24585,7 @@
       <c r="AE241" s="1"/>
       <c r="AF241" s="1"/>
       <c r="AG241" s="1"/>
-      <c r="AH241" s="1"/>
+      <c r="AH241" s="25"/>
       <c r="AI241" s="1"/>
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
@@ -24621,7 +24637,7 @@
       <c r="AE242" s="1"/>
       <c r="AF242" s="1"/>
       <c r="AG242" s="1"/>
-      <c r="AH242" s="1"/>
+      <c r="AH242" s="25"/>
       <c r="AI242" s="1"/>
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
@@ -24673,7 +24689,7 @@
       <c r="AE243" s="1"/>
       <c r="AF243" s="1"/>
       <c r="AG243" s="1"/>
-      <c r="AH243" s="1"/>
+      <c r="AH243" s="25"/>
       <c r="AI243" s="1"/>
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
@@ -24725,7 +24741,7 @@
       <c r="AE244" s="1"/>
       <c r="AF244" s="1"/>
       <c r="AG244" s="1"/>
-      <c r="AH244" s="1"/>
+      <c r="AH244" s="25"/>
       <c r="AI244" s="1"/>
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
@@ -24777,7 +24793,7 @@
       <c r="AE245" s="1"/>
       <c r="AF245" s="1"/>
       <c r="AG245" s="1"/>
-      <c r="AH245" s="1"/>
+      <c r="AH245" s="25"/>
       <c r="AI245" s="1"/>
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
@@ -24829,7 +24845,7 @@
       <c r="AE246" s="1"/>
       <c r="AF246" s="1"/>
       <c r="AG246" s="1"/>
-      <c r="AH246" s="1"/>
+      <c r="AH246" s="25"/>
       <c r="AI246" s="1"/>
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
@@ -24881,7 +24897,7 @@
       <c r="AE247" s="1"/>
       <c r="AF247" s="1"/>
       <c r="AG247" s="1"/>
-      <c r="AH247" s="1"/>
+      <c r="AH247" s="25"/>
       <c r="AI247" s="1"/>
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
@@ -24933,7 +24949,7 @@
       <c r="AE248" s="1"/>
       <c r="AF248" s="1"/>
       <c r="AG248" s="1"/>
-      <c r="AH248" s="1"/>
+      <c r="AH248" s="25"/>
       <c r="AI248" s="1"/>
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
@@ -24985,7 +25001,7 @@
       <c r="AE249" s="1"/>
       <c r="AF249" s="1"/>
       <c r="AG249" s="1"/>
-      <c r="AH249" s="1"/>
+      <c r="AH249" s="25"/>
       <c r="AI249" s="1"/>
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
@@ -25037,7 +25053,7 @@
       <c r="AE250" s="1"/>
       <c r="AF250" s="1"/>
       <c r="AG250" s="1"/>
-      <c r="AH250" s="1"/>
+      <c r="AH250" s="25"/>
       <c r="AI250" s="1"/>
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
@@ -25089,7 +25105,7 @@
       <c r="AE251" s="1"/>
       <c r="AF251" s="1"/>
       <c r="AG251" s="1"/>
-      <c r="AH251" s="1"/>
+      <c r="AH251" s="25"/>
       <c r="AI251" s="1"/>
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
@@ -25141,7 +25157,7 @@
       <c r="AE252" s="1"/>
       <c r="AF252" s="1"/>
       <c r="AG252" s="1"/>
-      <c r="AH252" s="1"/>
+      <c r="AH252" s="25"/>
       <c r="AI252" s="1"/>
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
@@ -25193,7 +25209,7 @@
       <c r="AE253" s="1"/>
       <c r="AF253" s="1"/>
       <c r="AG253" s="1"/>
-      <c r="AH253" s="1"/>
+      <c r="AH253" s="25"/>
       <c r="AI253" s="1"/>
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
@@ -25245,7 +25261,7 @@
       <c r="AE254" s="1"/>
       <c r="AF254" s="1"/>
       <c r="AG254" s="1"/>
-      <c r="AH254" s="1"/>
+      <c r="AH254" s="25"/>
       <c r="AI254" s="1"/>
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
@@ -25297,7 +25313,7 @@
       <c r="AE255" s="1"/>
       <c r="AF255" s="1"/>
       <c r="AG255" s="1"/>
-      <c r="AH255" s="1"/>
+      <c r="AH255" s="25"/>
       <c r="AI255" s="1"/>
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
@@ -25349,7 +25365,7 @@
       <c r="AE256" s="1"/>
       <c r="AF256" s="1"/>
       <c r="AG256" s="1"/>
-      <c r="AH256" s="1"/>
+      <c r="AH256" s="25"/>
       <c r="AI256" s="1"/>
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
@@ -25401,7 +25417,7 @@
       <c r="AE257" s="1"/>
       <c r="AF257" s="1"/>
       <c r="AG257" s="1"/>
-      <c r="AH257" s="1"/>
+      <c r="AH257" s="25"/>
       <c r="AI257" s="1"/>
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
@@ -25453,7 +25469,7 @@
       <c r="AE258" s="1"/>
       <c r="AF258" s="1"/>
       <c r="AG258" s="1"/>
-      <c r="AH258" s="1"/>
+      <c r="AH258" s="25"/>
       <c r="AI258" s="1"/>
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
@@ -25505,7 +25521,7 @@
       <c r="AE259" s="1"/>
       <c r="AF259" s="1"/>
       <c r="AG259" s="1"/>
-      <c r="AH259" s="1"/>
+      <c r="AH259" s="25"/>
       <c r="AI259" s="1"/>
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
@@ -25557,7 +25573,7 @@
       <c r="AE260" s="1"/>
       <c r="AF260" s="1"/>
       <c r="AG260" s="1"/>
-      <c r="AH260" s="1"/>
+      <c r="AH260" s="25"/>
       <c r="AI260" s="1"/>
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
@@ -25609,7 +25625,7 @@
       <c r="AE261" s="1"/>
       <c r="AF261" s="1"/>
       <c r="AG261" s="1"/>
-      <c r="AH261" s="1"/>
+      <c r="AH261" s="25"/>
       <c r="AI261" s="1"/>
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
@@ -25661,7 +25677,7 @@
       <c r="AE262" s="1"/>
       <c r="AF262" s="1"/>
       <c r="AG262" s="1"/>
-      <c r="AH262" s="1"/>
+      <c r="AH262" s="25"/>
       <c r="AI262" s="1"/>
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
@@ -25713,7 +25729,7 @@
       <c r="AE263" s="1"/>
       <c r="AF263" s="1"/>
       <c r="AG263" s="1"/>
-      <c r="AH263" s="1"/>
+      <c r="AH263" s="25"/>
       <c r="AI263" s="1"/>
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
@@ -25765,7 +25781,7 @@
       <c r="AE264" s="1"/>
       <c r="AF264" s="1"/>
       <c r="AG264" s="1"/>
-      <c r="AH264" s="1"/>
+      <c r="AH264" s="25"/>
       <c r="AI264" s="1"/>
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
@@ -25817,7 +25833,7 @@
       <c r="AE265" s="1"/>
       <c r="AF265" s="1"/>
       <c r="AG265" s="1"/>
-      <c r="AH265" s="1"/>
+      <c r="AH265" s="25"/>
       <c r="AI265" s="1"/>
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
@@ -25869,7 +25885,7 @@
       <c r="AE266" s="1"/>
       <c r="AF266" s="1"/>
       <c r="AG266" s="1"/>
-      <c r="AH266" s="1"/>
+      <c r="AH266" s="25"/>
       <c r="AI266" s="1"/>
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
@@ -25921,7 +25937,7 @@
       <c r="AE267" s="1"/>
       <c r="AF267" s="1"/>
       <c r="AG267" s="1"/>
-      <c r="AH267" s="1"/>
+      <c r="AH267" s="25"/>
       <c r="AI267" s="1"/>
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
@@ -25973,7 +25989,7 @@
       <c r="AE268" s="1"/>
       <c r="AF268" s="1"/>
       <c r="AG268" s="1"/>
-      <c r="AH268" s="1"/>
+      <c r="AH268" s="25"/>
       <c r="AI268" s="1"/>
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
@@ -26025,7 +26041,7 @@
       <c r="AE269" s="1"/>
       <c r="AF269" s="1"/>
       <c r="AG269" s="1"/>
-      <c r="AH269" s="1"/>
+      <c r="AH269" s="25"/>
       <c r="AI269" s="1"/>
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
@@ -26077,7 +26093,7 @@
       <c r="AE270" s="1"/>
       <c r="AF270" s="1"/>
       <c r="AG270" s="1"/>
-      <c r="AH270" s="1"/>
+      <c r="AH270" s="25"/>
       <c r="AI270" s="1"/>
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
@@ -26129,7 +26145,7 @@
       <c r="AE271" s="1"/>
       <c r="AF271" s="1"/>
       <c r="AG271" s="1"/>
-      <c r="AH271" s="1"/>
+      <c r="AH271" s="25"/>
       <c r="AI271" s="1"/>
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
@@ -26181,7 +26197,7 @@
       <c r="AE272" s="1"/>
       <c r="AF272" s="1"/>
       <c r="AG272" s="1"/>
-      <c r="AH272" s="1"/>
+      <c r="AH272" s="25"/>
       <c r="AI272" s="1"/>
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
@@ -26233,7 +26249,7 @@
       <c r="AE273" s="1"/>
       <c r="AF273" s="1"/>
       <c r="AG273" s="1"/>
-      <c r="AH273" s="1"/>
+      <c r="AH273" s="25"/>
       <c r="AI273" s="1"/>
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
@@ -26285,7 +26301,7 @@
       <c r="AE274" s="1"/>
       <c r="AF274" s="1"/>
       <c r="AG274" s="1"/>
-      <c r="AH274" s="1"/>
+      <c r="AH274" s="25"/>
       <c r="AI274" s="1"/>
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
@@ -26337,7 +26353,7 @@
       <c r="AE275" s="1"/>
       <c r="AF275" s="1"/>
       <c r="AG275" s="1"/>
-      <c r="AH275" s="1"/>
+      <c r="AH275" s="25"/>
       <c r="AI275" s="1"/>
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
@@ -26389,7 +26405,7 @@
       <c r="AE276" s="1"/>
       <c r="AF276" s="1"/>
       <c r="AG276" s="1"/>
-      <c r="AH276" s="1"/>
+      <c r="AH276" s="25"/>
       <c r="AI276" s="1"/>
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
@@ -26441,7 +26457,7 @@
       <c r="AE277" s="1"/>
       <c r="AF277" s="1"/>
       <c r="AG277" s="1"/>
-      <c r="AH277" s="1"/>
+      <c r="AH277" s="25"/>
       <c r="AI277" s="1"/>
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
@@ -26493,7 +26509,7 @@
       <c r="AE278" s="1"/>
       <c r="AF278" s="1"/>
       <c r="AG278" s="1"/>
-      <c r="AH278" s="1"/>
+      <c r="AH278" s="25"/>
       <c r="AI278" s="1"/>
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
@@ -26545,7 +26561,7 @@
       <c r="AE279" s="1"/>
       <c r="AF279" s="1"/>
       <c r="AG279" s="1"/>
-      <c r="AH279" s="1"/>
+      <c r="AH279" s="25"/>
       <c r="AI279" s="1"/>
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
@@ -26597,7 +26613,7 @@
       <c r="AE280" s="1"/>
       <c r="AF280" s="1"/>
       <c r="AG280" s="1"/>
-      <c r="AH280" s="1"/>
+      <c r="AH280" s="25"/>
       <c r="AI280" s="1"/>
       <c r="AJ280" s="1"/>
       <c r="AK280" s="1"/>
@@ -26649,7 +26665,7 @@
       <c r="AE281" s="1"/>
       <c r="AF281" s="1"/>
       <c r="AG281" s="1"/>
-      <c r="AH281" s="1"/>
+      <c r="AH281" s="25"/>
       <c r="AI281" s="1"/>
       <c r="AJ281" s="1"/>
       <c r="AK281" s="1"/>
@@ -26701,7 +26717,7 @@
       <c r="AE282" s="1"/>
       <c r="AF282" s="1"/>
       <c r="AG282" s="1"/>
-      <c r="AH282" s="1"/>
+      <c r="AH282" s="25"/>
       <c r="AI282" s="1"/>
       <c r="AJ282" s="1"/>
       <c r="AK282" s="1"/>
@@ -26753,7 +26769,7 @@
       <c r="AE283" s="1"/>
       <c r="AF283" s="1"/>
       <c r="AG283" s="1"/>
-      <c r="AH283" s="1"/>
+      <c r="AH283" s="25"/>
       <c r="AI283" s="1"/>
       <c r="AJ283" s="1"/>
       <c r="AK283" s="1"/>
@@ -26805,7 +26821,7 @@
       <c r="AE284" s="1"/>
       <c r="AF284" s="1"/>
       <c r="AG284" s="1"/>
-      <c r="AH284" s="1"/>
+      <c r="AH284" s="25"/>
       <c r="AI284" s="1"/>
       <c r="AJ284" s="1"/>
       <c r="AK284" s="1"/>
@@ -26857,7 +26873,7 @@
       <c r="AE285" s="1"/>
       <c r="AF285" s="1"/>
       <c r="AG285" s="1"/>
-      <c r="AH285" s="1"/>
+      <c r="AH285" s="25"/>
       <c r="AI285" s="1"/>
       <c r="AJ285" s="1"/>
       <c r="AK285" s="1"/>
@@ -26909,7 +26925,7 @@
       <c r="AE286" s="1"/>
       <c r="AF286" s="1"/>
       <c r="AG286" s="1"/>
-      <c r="AH286" s="1"/>
+      <c r="AH286" s="25"/>
       <c r="AI286" s="1"/>
       <c r="AJ286" s="1"/>
       <c r="AK286" s="1"/>
@@ -26961,7 +26977,7 @@
       <c r="AE287" s="1"/>
       <c r="AF287" s="1"/>
       <c r="AG287" s="1"/>
-      <c r="AH287" s="1"/>
+      <c r="AH287" s="25"/>
       <c r="AI287" s="1"/>
       <c r="AJ287" s="1"/>
       <c r="AK287" s="1"/>
@@ -27013,7 +27029,7 @@
       <c r="AE288" s="1"/>
       <c r="AF288" s="1"/>
       <c r="AG288" s="1"/>
-      <c r="AH288" s="1"/>
+      <c r="AH288" s="25"/>
       <c r="AI288" s="1"/>
       <c r="AJ288" s="1"/>
       <c r="AK288" s="1"/>
@@ -27065,7 +27081,7 @@
       <c r="AE289" s="1"/>
       <c r="AF289" s="1"/>
       <c r="AG289" s="1"/>
-      <c r="AH289" s="1"/>
+      <c r="AH289" s="25"/>
       <c r="AI289" s="1"/>
       <c r="AJ289" s="1"/>
       <c r="AK289" s="1"/>
@@ -27117,7 +27133,7 @@
       <c r="AE290" s="1"/>
       <c r="AF290" s="1"/>
       <c r="AG290" s="1"/>
-      <c r="AH290" s="1"/>
+      <c r="AH290" s="25"/>
       <c r="AI290" s="1"/>
       <c r="AJ290" s="1"/>
       <c r="AK290" s="1"/>
@@ -27169,7 +27185,7 @@
       <c r="AE291" s="1"/>
       <c r="AF291" s="1"/>
       <c r="AG291" s="1"/>
-      <c r="AH291" s="1"/>
+      <c r="AH291" s="25"/>
       <c r="AI291" s="1"/>
       <c r="AJ291" s="1"/>
       <c r="AK291" s="1"/>
@@ -27221,7 +27237,7 @@
       <c r="AE292" s="1"/>
       <c r="AF292" s="1"/>
       <c r="AG292" s="1"/>
-      <c r="AH292" s="1"/>
+      <c r="AH292" s="25"/>
       <c r="AI292" s="1"/>
       <c r="AJ292" s="1"/>
       <c r="AK292" s="1"/>
@@ -27273,7 +27289,7 @@
       <c r="AE293" s="1"/>
       <c r="AF293" s="1"/>
       <c r="AG293" s="1"/>
-      <c r="AH293" s="1"/>
+      <c r="AH293" s="25"/>
       <c r="AI293" s="1"/>
       <c r="AJ293" s="1"/>
       <c r="AK293" s="1"/>
@@ -27325,7 +27341,7 @@
       <c r="AE294" s="1"/>
       <c r="AF294" s="1"/>
       <c r="AG294" s="1"/>
-      <c r="AH294" s="1"/>
+      <c r="AH294" s="25"/>
       <c r="AI294" s="1"/>
       <c r="AJ294" s="1"/>
       <c r="AK294" s="1"/>
@@ -27377,7 +27393,7 @@
       <c r="AE295" s="1"/>
       <c r="AF295" s="1"/>
       <c r="AG295" s="1"/>
-      <c r="AH295" s="1"/>
+      <c r="AH295" s="25"/>
       <c r="AI295" s="1"/>
       <c r="AJ295" s="1"/>
       <c r="AK295" s="1"/>
@@ -27429,7 +27445,7 @@
       <c r="AE296" s="1"/>
       <c r="AF296" s="1"/>
       <c r="AG296" s="1"/>
-      <c r="AH296" s="1"/>
+      <c r="AH296" s="25"/>
       <c r="AI296" s="1"/>
       <c r="AJ296" s="1"/>
       <c r="AK296" s="1"/>
@@ -27481,7 +27497,7 @@
       <c r="AE297" s="1"/>
       <c r="AF297" s="1"/>
       <c r="AG297" s="1"/>
-      <c r="AH297" s="1"/>
+      <c r="AH297" s="25"/>
       <c r="AI297" s="1"/>
       <c r="AJ297" s="1"/>
       <c r="AK297" s="1"/>
@@ -27533,7 +27549,7 @@
       <c r="AE298" s="1"/>
       <c r="AF298" s="1"/>
       <c r="AG298" s="1"/>
-      <c r="AH298" s="1"/>
+      <c r="AH298" s="25"/>
       <c r="AI298" s="1"/>
       <c r="AJ298" s="1"/>
       <c r="AK298" s="1"/>
@@ -27585,7 +27601,7 @@
       <c r="AE299" s="1"/>
       <c r="AF299" s="1"/>
       <c r="AG299" s="1"/>
-      <c r="AH299" s="1"/>
+      <c r="AH299" s="25"/>
       <c r="AI299" s="1"/>
       <c r="AJ299" s="1"/>
       <c r="AK299" s="1"/>
@@ -27637,7 +27653,7 @@
       <c r="AE300" s="1"/>
       <c r="AF300" s="1"/>
       <c r="AG300" s="1"/>
-      <c r="AH300" s="1"/>
+      <c r="AH300" s="25"/>
       <c r="AI300" s="1"/>
       <c r="AJ300" s="1"/>
       <c r="AK300" s="1"/>
@@ -27689,7 +27705,7 @@
       <c r="AE301" s="1"/>
       <c r="AF301" s="1"/>
       <c r="AG301" s="1"/>
-      <c r="AH301" s="1"/>
+      <c r="AH301" s="25"/>
       <c r="AI301" s="1"/>
       <c r="AJ301" s="1"/>
       <c r="AK301" s="1"/>
@@ -27741,7 +27757,7 @@
       <c r="AE302" s="1"/>
       <c r="AF302" s="1"/>
       <c r="AG302" s="1"/>
-      <c r="AH302" s="1"/>
+      <c r="AH302" s="25"/>
       <c r="AI302" s="1"/>
       <c r="AJ302" s="1"/>
       <c r="AK302" s="1"/>
@@ -27793,7 +27809,7 @@
       <c r="AE303" s="1"/>
       <c r="AF303" s="1"/>
       <c r="AG303" s="1"/>
-      <c r="AH303" s="1"/>
+      <c r="AH303" s="25"/>
       <c r="AI303" s="1"/>
       <c r="AJ303" s="1"/>
       <c r="AK303" s="1"/>
@@ -27845,7 +27861,7 @@
       <c r="AE304" s="1"/>
       <c r="AF304" s="1"/>
       <c r="AG304" s="1"/>
-      <c r="AH304" s="1"/>
+      <c r="AH304" s="25"/>
       <c r="AI304" s="1"/>
       <c r="AJ304" s="1"/>
       <c r="AK304" s="1"/>
@@ -27897,7 +27913,7 @@
       <c r="AE305" s="1"/>
       <c r="AF305" s="1"/>
       <c r="AG305" s="1"/>
-      <c r="AH305" s="1"/>
+      <c r="AH305" s="25"/>
       <c r="AI305" s="1"/>
       <c r="AJ305" s="1"/>
       <c r="AK305" s="1"/>
@@ -27949,7 +27965,7 @@
       <c r="AE306" s="1"/>
       <c r="AF306" s="1"/>
       <c r="AG306" s="1"/>
-      <c r="AH306" s="1"/>
+      <c r="AH306" s="25"/>
       <c r="AI306" s="1"/>
       <c r="AJ306" s="1"/>
       <c r="AK306" s="1"/>
@@ -28001,7 +28017,7 @@
       <c r="AE307" s="1"/>
       <c r="AF307" s="1"/>
       <c r="AG307" s="1"/>
-      <c r="AH307" s="1"/>
+      <c r="AH307" s="25"/>
       <c r="AI307" s="1"/>
       <c r="AJ307" s="1"/>
       <c r="AK307" s="1"/>
@@ -28053,7 +28069,7 @@
       <c r="AE308" s="1"/>
       <c r="AF308" s="1"/>
       <c r="AG308" s="1"/>
-      <c r="AH308" s="1"/>
+      <c r="AH308" s="25"/>
       <c r="AI308" s="1"/>
       <c r="AJ308" s="1"/>
       <c r="AK308" s="1"/>
@@ -28105,7 +28121,7 @@
       <c r="AE309" s="1"/>
       <c r="AF309" s="1"/>
       <c r="AG309" s="1"/>
-      <c r="AH309" s="1"/>
+      <c r="AH309" s="25"/>
       <c r="AI309" s="1"/>
       <c r="AJ309" s="1"/>
       <c r="AK309" s="1"/>
@@ -28157,7 +28173,7 @@
       <c r="AE310" s="1"/>
       <c r="AF310" s="1"/>
       <c r="AG310" s="1"/>
-      <c r="AH310" s="1"/>
+      <c r="AH310" s="25"/>
       <c r="AI310" s="1"/>
       <c r="AJ310" s="1"/>
       <c r="AK310" s="1"/>
@@ -28209,7 +28225,7 @@
       <c r="AE311" s="1"/>
       <c r="AF311" s="1"/>
       <c r="AG311" s="1"/>
-      <c r="AH311" s="1"/>
+      <c r="AH311" s="25"/>
       <c r="AI311" s="1"/>
       <c r="AJ311" s="1"/>
       <c r="AK311" s="1"/>
@@ -28261,7 +28277,7 @@
       <c r="AE312" s="1"/>
       <c r="AF312" s="1"/>
       <c r="AG312" s="1"/>
-      <c r="AH312" s="1"/>
+      <c r="AH312" s="25"/>
       <c r="AI312" s="1"/>
       <c r="AJ312" s="1"/>
       <c r="AK312" s="1"/>
@@ -28313,7 +28329,7 @@
       <c r="AE313" s="1"/>
       <c r="AF313" s="1"/>
       <c r="AG313" s="1"/>
-      <c r="AH313" s="1"/>
+      <c r="AH313" s="25"/>
       <c r="AI313" s="1"/>
       <c r="AJ313" s="1"/>
       <c r="AK313" s="1"/>
@@ -28365,7 +28381,7 @@
       <c r="AE314" s="1"/>
       <c r="AF314" s="1"/>
       <c r="AG314" s="1"/>
-      <c r="AH314" s="1"/>
+      <c r="AH314" s="25"/>
       <c r="AI314" s="1"/>
       <c r="AJ314" s="1"/>
       <c r="AK314" s="1"/>
@@ -28417,7 +28433,7 @@
       <c r="AE315" s="1"/>
       <c r="AF315" s="1"/>
       <c r="AG315" s="1"/>
-      <c r="AH315" s="1"/>
+      <c r="AH315" s="25"/>
       <c r="AI315" s="1"/>
       <c r="AJ315" s="1"/>
       <c r="AK315" s="1"/>
@@ -28469,7 +28485,7 @@
       <c r="AE316" s="1"/>
       <c r="AF316" s="1"/>
       <c r="AG316" s="1"/>
-      <c r="AH316" s="1"/>
+      <c r="AH316" s="25"/>
       <c r="AI316" s="1"/>
       <c r="AJ316" s="1"/>
       <c r="AK316" s="1"/>
@@ -28521,7 +28537,7 @@
       <c r="AE317" s="1"/>
       <c r="AF317" s="1"/>
       <c r="AG317" s="1"/>
-      <c r="AH317" s="1"/>
+      <c r="AH317" s="25"/>
       <c r="AI317" s="1"/>
       <c r="AJ317" s="1"/>
       <c r="AK317" s="1"/>
@@ -28573,7 +28589,7 @@
       <c r="AE318" s="1"/>
       <c r="AF318" s="1"/>
       <c r="AG318" s="1"/>
-      <c r="AH318" s="1"/>
+      <c r="AH318" s="25"/>
       <c r="AI318" s="1"/>
       <c r="AJ318" s="1"/>
       <c r="AK318" s="1"/>
@@ -28625,7 +28641,7 @@
       <c r="AE319" s="1"/>
       <c r="AF319" s="1"/>
       <c r="AG319" s="1"/>
-      <c r="AH319" s="1"/>
+      <c r="AH319" s="25"/>
       <c r="AI319" s="1"/>
       <c r="AJ319" s="1"/>
       <c r="AK319" s="1"/>
@@ -28677,7 +28693,7 @@
       <c r="AE320" s="1"/>
       <c r="AF320" s="1"/>
       <c r="AG320" s="1"/>
-      <c r="AH320" s="1"/>
+      <c r="AH320" s="25"/>
       <c r="AI320" s="1"/>
       <c r="AJ320" s="1"/>
       <c r="AK320" s="1"/>
@@ -28729,7 +28745,7 @@
       <c r="AE321" s="1"/>
       <c r="AF321" s="1"/>
       <c r="AG321" s="1"/>
-      <c r="AH321" s="1"/>
+      <c r="AH321" s="25"/>
       <c r="AI321" s="1"/>
       <c r="AJ321" s="1"/>
       <c r="AK321" s="1"/>
@@ -28781,7 +28797,7 @@
       <c r="AE322" s="1"/>
       <c r="AF322" s="1"/>
       <c r="AG322" s="1"/>
-      <c r="AH322" s="1"/>
+      <c r="AH322" s="25"/>
       <c r="AI322" s="1"/>
       <c r="AJ322" s="1"/>
       <c r="AK322" s="1"/>
@@ -28833,7 +28849,7 @@
       <c r="AE323" s="1"/>
       <c r="AF323" s="1"/>
       <c r="AG323" s="1"/>
-      <c r="AH323" s="1"/>
+      <c r="AH323" s="25"/>
       <c r="AI323" s="1"/>
       <c r="AJ323" s="1"/>
       <c r="AK323" s="1"/>
@@ -28885,7 +28901,7 @@
       <c r="AE324" s="1"/>
       <c r="AF324" s="1"/>
       <c r="AG324" s="1"/>
-      <c r="AH324" s="1"/>
+      <c r="AH324" s="25"/>
       <c r="AI324" s="1"/>
       <c r="AJ324" s="1"/>
       <c r="AK324" s="1"/>
@@ -28937,7 +28953,7 @@
       <c r="AE325" s="1"/>
       <c r="AF325" s="1"/>
       <c r="AG325" s="1"/>
-      <c r="AH325" s="1"/>
+      <c r="AH325" s="25"/>
       <c r="AI325" s="1"/>
       <c r="AJ325" s="1"/>
       <c r="AK325" s="1"/>
@@ -28989,7 +29005,7 @@
       <c r="AE326" s="1"/>
       <c r="AF326" s="1"/>
       <c r="AG326" s="1"/>
-      <c r="AH326" s="1"/>
+      <c r="AH326" s="25"/>
       <c r="AI326" s="1"/>
       <c r="AJ326" s="1"/>
       <c r="AK326" s="1"/>
@@ -29041,7 +29057,7 @@
       <c r="AE327" s="1"/>
       <c r="AF327" s="1"/>
       <c r="AG327" s="1"/>
-      <c r="AH327" s="1"/>
+      <c r="AH327" s="25"/>
       <c r="AI327" s="1"/>
       <c r="AJ327" s="1"/>
       <c r="AK327" s="1"/>
@@ -29093,7 +29109,7 @@
       <c r="AE328" s="1"/>
       <c r="AF328" s="1"/>
       <c r="AG328" s="1"/>
-      <c r="AH328" s="1"/>
+      <c r="AH328" s="25"/>
       <c r="AI328" s="1"/>
       <c r="AJ328" s="1"/>
       <c r="AK328" s="1"/>
@@ -29145,7 +29161,7 @@
       <c r="AE329" s="1"/>
       <c r="AF329" s="1"/>
       <c r="AG329" s="1"/>
-      <c r="AH329" s="1"/>
+      <c r="AH329" s="25"/>
       <c r="AI329" s="1"/>
       <c r="AJ329" s="1"/>
       <c r="AK329" s="1"/>
@@ -29197,7 +29213,7 @@
       <c r="AE330" s="1"/>
       <c r="AF330" s="1"/>
       <c r="AG330" s="1"/>
-      <c r="AH330" s="1"/>
+      <c r="AH330" s="25"/>
       <c r="AI330" s="1"/>
       <c r="AJ330" s="1"/>
       <c r="AK330" s="1"/>
@@ -29249,7 +29265,7 @@
       <c r="AE331" s="1"/>
       <c r="AF331" s="1"/>
       <c r="AG331" s="1"/>
-      <c r="AH331" s="1"/>
+      <c r="AH331" s="25"/>
       <c r="AI331" s="1"/>
       <c r="AJ331" s="1"/>
       <c r="AK331" s="1"/>
@@ -29301,7 +29317,7 @@
       <c r="AE332" s="1"/>
       <c r="AF332" s="1"/>
       <c r="AG332" s="1"/>
-      <c r="AH332" s="1"/>
+      <c r="AH332" s="25"/>
       <c r="AI332" s="1"/>
       <c r="AJ332" s="1"/>
       <c r="AK332" s="1"/>
@@ -29353,7 +29369,7 @@
       <c r="AE333" s="1"/>
       <c r="AF333" s="1"/>
       <c r="AG333" s="1"/>
-      <c r="AH333" s="1"/>
+      <c r="AH333" s="25"/>
       <c r="AI333" s="1"/>
       <c r="AJ333" s="1"/>
       <c r="AK333" s="1"/>
@@ -29405,7 +29421,7 @@
       <c r="AE334" s="1"/>
       <c r="AF334" s="1"/>
       <c r="AG334" s="1"/>
-      <c r="AH334" s="1"/>
+      <c r="AH334" s="25"/>
       <c r="AI334" s="1"/>
       <c r="AJ334" s="1"/>
       <c r="AK334" s="1"/>
@@ -29457,7 +29473,7 @@
       <c r="AE335" s="1"/>
       <c r="AF335" s="1"/>
       <c r="AG335" s="1"/>
-      <c r="AH335" s="1"/>
+      <c r="AH335" s="25"/>
       <c r="AI335" s="1"/>
       <c r="AJ335" s="1"/>
       <c r="AK335" s="1"/>
@@ -29509,7 +29525,7 @@
       <c r="AE336" s="1"/>
       <c r="AF336" s="1"/>
       <c r="AG336" s="1"/>
-      <c r="AH336" s="1"/>
+      <c r="AH336" s="25"/>
       <c r="AI336" s="1"/>
       <c r="AJ336" s="1"/>
       <c r="AK336" s="1"/>
@@ -29561,7 +29577,7 @@
       <c r="AE337" s="1"/>
       <c r="AF337" s="1"/>
       <c r="AG337" s="1"/>
-      <c r="AH337" s="1"/>
+      <c r="AH337" s="25"/>
       <c r="AI337" s="1"/>
       <c r="AJ337" s="1"/>
       <c r="AK337" s="1"/>
@@ -29613,7 +29629,7 @@
       <c r="AE338" s="1"/>
       <c r="AF338" s="1"/>
       <c r="AG338" s="1"/>
-      <c r="AH338" s="1"/>
+      <c r="AH338" s="25"/>
       <c r="AI338" s="1"/>
       <c r="AJ338" s="1"/>
       <c r="AK338" s="1"/>
@@ -29665,7 +29681,7 @@
       <c r="AE339" s="1"/>
       <c r="AF339" s="1"/>
       <c r="AG339" s="1"/>
-      <c r="AH339" s="1"/>
+      <c r="AH339" s="25"/>
       <c r="AI339" s="1"/>
       <c r="AJ339" s="1"/>
       <c r="AK339" s="1"/>
@@ -29717,7 +29733,7 @@
       <c r="AE340" s="1"/>
       <c r="AF340" s="1"/>
       <c r="AG340" s="1"/>
-      <c r="AH340" s="1"/>
+      <c r="AH340" s="25"/>
       <c r="AI340" s="1"/>
       <c r="AJ340" s="1"/>
       <c r="AK340" s="1"/>
@@ -29769,7 +29785,7 @@
       <c r="AE341" s="1"/>
       <c r="AF341" s="1"/>
       <c r="AG341" s="1"/>
-      <c r="AH341" s="1"/>
+      <c r="AH341" s="25"/>
       <c r="AI341" s="1"/>
       <c r="AJ341" s="1"/>
       <c r="AK341" s="1"/>
@@ -29821,7 +29837,7 @@
       <c r="AE342" s="1"/>
       <c r="AF342" s="1"/>
       <c r="AG342" s="1"/>
-      <c r="AH342" s="1"/>
+      <c r="AH342" s="25"/>
       <c r="AI342" s="1"/>
       <c r="AJ342" s="1"/>
       <c r="AK342" s="1"/>
@@ -29873,7 +29889,7 @@
       <c r="AE343" s="1"/>
       <c r="AF343" s="1"/>
       <c r="AG343" s="1"/>
-      <c r="AH343" s="1"/>
+      <c r="AH343" s="25"/>
       <c r="AI343" s="1"/>
       <c r="AJ343" s="1"/>
       <c r="AK343" s="1"/>
@@ -29925,7 +29941,7 @@
       <c r="AE344" s="1"/>
       <c r="AF344" s="1"/>
       <c r="AG344" s="1"/>
-      <c r="AH344" s="1"/>
+      <c r="AH344" s="25"/>
       <c r="AI344" s="1"/>
       <c r="AJ344" s="1"/>
       <c r="AK344" s="1"/>
@@ -29977,7 +29993,7 @@
       <c r="AE345" s="1"/>
       <c r="AF345" s="1"/>
       <c r="AG345" s="1"/>
-      <c r="AH345" s="1"/>
+      <c r="AH345" s="25"/>
       <c r="AI345" s="1"/>
       <c r="AJ345" s="1"/>
       <c r="AK345" s="1"/>
@@ -30029,7 +30045,7 @@
       <c r="AE346" s="1"/>
       <c r="AF346" s="1"/>
       <c r="AG346" s="1"/>
-      <c r="AH346" s="1"/>
+      <c r="AH346" s="25"/>
       <c r="AI346" s="1"/>
       <c r="AJ346" s="1"/>
       <c r="AK346" s="1"/>
@@ -30081,7 +30097,7 @@
       <c r="AE347" s="1"/>
       <c r="AF347" s="1"/>
       <c r="AG347" s="1"/>
-      <c r="AH347" s="1"/>
+      <c r="AH347" s="25"/>
       <c r="AI347" s="1"/>
       <c r="AJ347" s="1"/>
       <c r="AK347" s="1"/>
@@ -30133,7 +30149,7 @@
       <c r="AE348" s="1"/>
       <c r="AF348" s="1"/>
       <c r="AG348" s="1"/>
-      <c r="AH348" s="1"/>
+      <c r="AH348" s="25"/>
       <c r="AI348" s="1"/>
       <c r="AJ348" s="1"/>
       <c r="AK348" s="1"/>
@@ -30185,7 +30201,7 @@
       <c r="AE349" s="1"/>
       <c r="AF349" s="1"/>
       <c r="AG349" s="1"/>
-      <c r="AH349" s="1"/>
+      <c r="AH349" s="25"/>
       <c r="AI349" s="1"/>
       <c r="AJ349" s="1"/>
       <c r="AK349" s="1"/>
@@ -30237,7 +30253,7 @@
       <c r="AE350" s="1"/>
       <c r="AF350" s="1"/>
       <c r="AG350" s="1"/>
-      <c r="AH350" s="1"/>
+      <c r="AH350" s="25"/>
       <c r="AI350" s="1"/>
       <c r="AJ350" s="1"/>
       <c r="AK350" s="1"/>
@@ -30289,7 +30305,7 @@
       <c r="AE351" s="1"/>
       <c r="AF351" s="1"/>
       <c r="AG351" s="1"/>
-      <c r="AH351" s="1"/>
+      <c r="AH351" s="25"/>
       <c r="AI351" s="1"/>
       <c r="AJ351" s="1"/>
       <c r="AK351" s="1"/>
@@ -30341,7 +30357,7 @@
       <c r="AE352" s="1"/>
       <c r="AF352" s="1"/>
       <c r="AG352" s="1"/>
-      <c r="AH352" s="1"/>
+      <c r="AH352" s="25"/>
       <c r="AI352" s="1"/>
       <c r="AJ352" s="1"/>
       <c r="AK352" s="1"/>
@@ -30393,7 +30409,7 @@
       <c r="AE353" s="1"/>
       <c r="AF353" s="1"/>
       <c r="AG353" s="1"/>
-      <c r="AH353" s="1"/>
+      <c r="AH353" s="25"/>
       <c r="AI353" s="1"/>
       <c r="AJ353" s="1"/>
       <c r="AK353" s="1"/>
@@ -30445,7 +30461,7 @@
       <c r="AE354" s="1"/>
       <c r="AF354" s="1"/>
       <c r="AG354" s="1"/>
-      <c r="AH354" s="1"/>
+      <c r="AH354" s="25"/>
       <c r="AI354" s="1"/>
       <c r="AJ354" s="1"/>
       <c r="AK354" s="1"/>
@@ -30497,7 +30513,7 @@
       <c r="AE355" s="1"/>
       <c r="AF355" s="1"/>
       <c r="AG355" s="1"/>
-      <c r="AH355" s="1"/>
+      <c r="AH355" s="25"/>
       <c r="AI355" s="1"/>
       <c r="AJ355" s="1"/>
       <c r="AK355" s="1"/>
@@ -30549,7 +30565,7 @@
       <c r="AE356" s="1"/>
       <c r="AF356" s="1"/>
       <c r="AG356" s="1"/>
-      <c r="AH356" s="1"/>
+      <c r="AH356" s="25"/>
       <c r="AI356" s="1"/>
       <c r="AJ356" s="1"/>
       <c r="AK356" s="1"/>
@@ -30601,7 +30617,7 @@
       <c r="AE357" s="1"/>
       <c r="AF357" s="1"/>
       <c r="AG357" s="1"/>
-      <c r="AH357" s="1"/>
+      <c r="AH357" s="25"/>
       <c r="AI357" s="1"/>
       <c r="AJ357" s="1"/>
       <c r="AK357" s="1"/>
@@ -30653,7 +30669,7 @@
       <c r="AE358" s="1"/>
       <c r="AF358" s="1"/>
       <c r="AG358" s="1"/>
-      <c r="AH358" s="1"/>
+      <c r="AH358" s="25"/>
       <c r="AI358" s="1"/>
       <c r="AJ358" s="1"/>
       <c r="AK358" s="1"/>
@@ -30705,7 +30721,7 @@
       <c r="AE359" s="1"/>
       <c r="AF359" s="1"/>
       <c r="AG359" s="1"/>
-      <c r="AH359" s="1"/>
+      <c r="AH359" s="25"/>
       <c r="AI359" s="1"/>
       <c r="AJ359" s="1"/>
       <c r="AK359" s="1"/>
@@ -30757,7 +30773,7 @@
       <c r="AE360" s="1"/>
       <c r="AF360" s="1"/>
       <c r="AG360" s="1"/>
-      <c r="AH360" s="1"/>
+      <c r="AH360" s="25"/>
       <c r="AI360" s="1"/>
       <c r="AJ360" s="1"/>
       <c r="AK360" s="1"/>
@@ -30809,7 +30825,7 @@
       <c r="AE361" s="1"/>
       <c r="AF361" s="1"/>
       <c r="AG361" s="1"/>
-      <c r="AH361" s="1"/>
+      <c r="AH361" s="25"/>
       <c r="AI361" s="1"/>
       <c r="AJ361" s="1"/>
       <c r="AK361" s="1"/>
@@ -30861,7 +30877,7 @@
       <c r="AE362" s="1"/>
       <c r="AF362" s="1"/>
       <c r="AG362" s="1"/>
-      <c r="AH362" s="1"/>
+      <c r="AH362" s="25"/>
       <c r="AI362" s="1"/>
       <c r="AJ362" s="1"/>
       <c r="AK362" s="1"/>
@@ -30913,7 +30929,7 @@
       <c r="AE363" s="1"/>
       <c r="AF363" s="1"/>
       <c r="AG363" s="1"/>
-      <c r="AH363" s="1"/>
+      <c r="AH363" s="25"/>
       <c r="AI363" s="1"/>
       <c r="AJ363" s="1"/>
       <c r="AK363" s="1"/>
@@ -30965,7 +30981,7 @@
       <c r="AE364" s="1"/>
       <c r="AF364" s="1"/>
       <c r="AG364" s="1"/>
-      <c r="AH364" s="1"/>
+      <c r="AH364" s="25"/>
       <c r="AI364" s="1"/>
       <c r="AJ364" s="1"/>
       <c r="AK364" s="1"/>
@@ -31017,7 +31033,7 @@
       <c r="AE365" s="1"/>
       <c r="AF365" s="1"/>
       <c r="AG365" s="1"/>
-      <c r="AH365" s="1"/>
+      <c r="AH365" s="25"/>
       <c r="AI365" s="1"/>
       <c r="AJ365" s="1"/>
       <c r="AK365" s="1"/>
@@ -31069,7 +31085,7 @@
       <c r="AE366" s="1"/>
       <c r="AF366" s="1"/>
       <c r="AG366" s="1"/>
-      <c r="AH366" s="1"/>
+      <c r="AH366" s="25"/>
       <c r="AI366" s="1"/>
       <c r="AJ366" s="1"/>
       <c r="AK366" s="1"/>
@@ -31121,7 +31137,7 @@
       <c r="AE367" s="1"/>
       <c r="AF367" s="1"/>
       <c r="AG367" s="1"/>
-      <c r="AH367" s="1"/>
+      <c r="AH367" s="25"/>
       <c r="AI367" s="1"/>
       <c r="AJ367" s="1"/>
       <c r="AK367" s="1"/>
@@ -31173,7 +31189,7 @@
       <c r="AE368" s="1"/>
       <c r="AF368" s="1"/>
       <c r="AG368" s="1"/>
-      <c r="AH368" s="1"/>
+      <c r="AH368" s="25"/>
       <c r="AI368" s="1"/>
       <c r="AJ368" s="1"/>
       <c r="AK368" s="1"/>
@@ -31225,7 +31241,7 @@
       <c r="AE369" s="1"/>
       <c r="AF369" s="1"/>
       <c r="AG369" s="1"/>
-      <c r="AH369" s="1"/>
+      <c r="AH369" s="25"/>
       <c r="AI369" s="1"/>
       <c r="AJ369" s="1"/>
       <c r="AK369" s="1"/>
@@ -31277,7 +31293,7 @@
       <c r="AE370" s="1"/>
       <c r="AF370" s="1"/>
       <c r="AG370" s="1"/>
-      <c r="AH370" s="1"/>
+      <c r="AH370" s="25"/>
       <c r="AI370" s="1"/>
       <c r="AJ370" s="1"/>
       <c r="AK370" s="1"/>
@@ -31329,7 +31345,7 @@
       <c r="AE371" s="1"/>
       <c r="AF371" s="1"/>
       <c r="AG371" s="1"/>
-      <c r="AH371" s="1"/>
+      <c r="AH371" s="25"/>
       <c r="AI371" s="1"/>
       <c r="AJ371" s="1"/>
       <c r="AK371" s="1"/>
@@ -31381,7 +31397,7 @@
       <c r="AE372" s="1"/>
       <c r="AF372" s="1"/>
       <c r="AG372" s="1"/>
-      <c r="AH372" s="1"/>
+      <c r="AH372" s="25"/>
       <c r="AI372" s="1"/>
       <c r="AJ372" s="1"/>
       <c r="AK372" s="1"/>
@@ -31433,7 +31449,7 @@
       <c r="AE373" s="1"/>
       <c r="AF373" s="1"/>
       <c r="AG373" s="1"/>
-      <c r="AH373" s="1"/>
+      <c r="AH373" s="25"/>
       <c r="AI373" s="1"/>
       <c r="AJ373" s="1"/>
       <c r="AK373" s="1"/>
@@ -31485,7 +31501,7 @@
       <c r="AE374" s="1"/>
       <c r="AF374" s="1"/>
       <c r="AG374" s="1"/>
-      <c r="AH374" s="1"/>
+      <c r="AH374" s="25"/>
       <c r="AI374" s="1"/>
       <c r="AJ374" s="1"/>
       <c r="AK374" s="1"/>
@@ -31537,7 +31553,7 @@
       <c r="AE375" s="1"/>
       <c r="AF375" s="1"/>
       <c r="AG375" s="1"/>
-      <c r="AH375" s="1"/>
+      <c r="AH375" s="25"/>
       <c r="AI375" s="1"/>
       <c r="AJ375" s="1"/>
       <c r="AK375" s="1"/>
@@ -31589,7 +31605,7 @@
       <c r="AE376" s="1"/>
       <c r="AF376" s="1"/>
       <c r="AG376" s="1"/>
-      <c r="AH376" s="1"/>
+      <c r="AH376" s="25"/>
       <c r="AI376" s="1"/>
       <c r="AJ376" s="1"/>
       <c r="AK376" s="1"/>
@@ -31641,7 +31657,7 @@
       <c r="AE377" s="1"/>
       <c r="AF377" s="1"/>
       <c r="AG377" s="1"/>
-      <c r="AH377" s="1"/>
+      <c r="AH377" s="25"/>
       <c r="AI377" s="1"/>
       <c r="AJ377" s="1"/>
       <c r="AK377" s="1"/>
@@ -31693,7 +31709,7 @@
       <c r="AE378" s="1"/>
       <c r="AF378" s="1"/>
       <c r="AG378" s="1"/>
-      <c r="AH378" s="1"/>
+      <c r="AH378" s="25"/>
       <c r="AI378" s="1"/>
       <c r="AJ378" s="1"/>
       <c r="AK378" s="1"/>
@@ -31745,7 +31761,7 @@
       <c r="AE379" s="1"/>
       <c r="AF379" s="1"/>
       <c r="AG379" s="1"/>
-      <c r="AH379" s="1"/>
+      <c r="AH379" s="25"/>
       <c r="AI379" s="1"/>
       <c r="AJ379" s="1"/>
       <c r="AK379" s="1"/>
@@ -31797,7 +31813,7 @@
       <c r="AE380" s="1"/>
       <c r="AF380" s="1"/>
       <c r="AG380" s="1"/>
-      <c r="AH380" s="1"/>
+      <c r="AH380" s="25"/>
       <c r="AI380" s="1"/>
       <c r="AJ380" s="1"/>
       <c r="AK380" s="1"/>
@@ -31849,7 +31865,7 @@
       <c r="AE381" s="1"/>
       <c r="AF381" s="1"/>
       <c r="AG381" s="1"/>
-      <c r="AH381" s="1"/>
+      <c r="AH381" s="25"/>
       <c r="AI381" s="1"/>
       <c r="AJ381" s="1"/>
       <c r="AK381" s="1"/>
@@ -31901,7 +31917,7 @@
       <c r="AE382" s="1"/>
       <c r="AF382" s="1"/>
       <c r="AG382" s="1"/>
-      <c r="AH382" s="1"/>
+      <c r="AH382" s="25"/>
       <c r="AI382" s="1"/>
       <c r="AJ382" s="1"/>
       <c r="AK382" s="1"/>
@@ -31953,7 +31969,7 @@
       <c r="AE383" s="1"/>
       <c r="AF383" s="1"/>
       <c r="AG383" s="1"/>
-      <c r="AH383" s="1"/>
+      <c r="AH383" s="25"/>
       <c r="AI383" s="1"/>
       <c r="AJ383" s="1"/>
       <c r="AK383" s="1"/>
@@ -32005,7 +32021,7 @@
       <c r="AE384" s="1"/>
       <c r="AF384" s="1"/>
       <c r="AG384" s="1"/>
-      <c r="AH384" s="1"/>
+      <c r="AH384" s="25"/>
       <c r="AI384" s="1"/>
       <c r="AJ384" s="1"/>
       <c r="AK384" s="1"/>
@@ -32057,7 +32073,7 @@
       <c r="AE385" s="1"/>
       <c r="AF385" s="1"/>
       <c r="AG385" s="1"/>
-      <c r="AH385" s="1"/>
+      <c r="AH385" s="25"/>
       <c r="AI385" s="1"/>
       <c r="AJ385" s="1"/>
       <c r="AK385" s="1"/>
@@ -32109,7 +32125,7 @@
       <c r="AE386" s="1"/>
       <c r="AF386" s="1"/>
       <c r="AG386" s="1"/>
-      <c r="AH386" s="1"/>
+      <c r="AH386" s="25"/>
       <c r="AI386" s="1"/>
       <c r="AJ386" s="1"/>
       <c r="AK386" s="1"/>
@@ -32161,7 +32177,7 @@
       <c r="AE387" s="1"/>
       <c r="AF387" s="1"/>
       <c r="AG387" s="1"/>
-      <c r="AH387" s="1"/>
+      <c r="AH387" s="25"/>
       <c r="AI387" s="1"/>
       <c r="AJ387" s="1"/>
       <c r="AK387" s="1"/>
@@ -32213,7 +32229,7 @@
       <c r="AE388" s="1"/>
       <c r="AF388" s="1"/>
       <c r="AG388" s="1"/>
-      <c r="AH388" s="1"/>
+      <c r="AH388" s="25"/>
       <c r="AI388" s="1"/>
       <c r="AJ388" s="1"/>
       <c r="AK388" s="1"/>
@@ -32265,7 +32281,7 @@
       <c r="AE389" s="1"/>
       <c r="AF389" s="1"/>
       <c r="AG389" s="1"/>
-      <c r="AH389" s="1"/>
+      <c r="AH389" s="25"/>
       <c r="AI389" s="1"/>
       <c r="AJ389" s="1"/>
       <c r="AK389" s="1"/>
@@ -32317,7 +32333,7 @@
       <c r="AE390" s="1"/>
       <c r="AF390" s="1"/>
       <c r="AG390" s="1"/>
-      <c r="AH390" s="1"/>
+      <c r="AH390" s="25"/>
       <c r="AI390" s="1"/>
       <c r="AJ390" s="1"/>
       <c r="AK390" s="1"/>
@@ -32369,7 +32385,7 @@
       <c r="AE391" s="1"/>
       <c r="AF391" s="1"/>
       <c r="AG391" s="1"/>
-      <c r="AH391" s="1"/>
+      <c r="AH391" s="25"/>
       <c r="AI391" s="1"/>
       <c r="AJ391" s="1"/>
       <c r="AK391" s="1"/>
@@ -32421,7 +32437,7 @@
       <c r="AE392" s="1"/>
       <c r="AF392" s="1"/>
       <c r="AG392" s="1"/>
-      <c r="AH392" s="1"/>
+      <c r="AH392" s="25"/>
       <c r="AI392" s="1"/>
       <c r="AJ392" s="1"/>
       <c r="AK392" s="1"/>
@@ -32473,7 +32489,7 @@
       <c r="AE393" s="1"/>
       <c r="AF393" s="1"/>
       <c r="AG393" s="1"/>
-      <c r="AH393" s="1"/>
+      <c r="AH393" s="25"/>
       <c r="AI393" s="1"/>
       <c r="AJ393" s="1"/>
       <c r="AK393" s="1"/>
@@ -32525,7 +32541,7 @@
       <c r="AE394" s="1"/>
       <c r="AF394" s="1"/>
       <c r="AG394" s="1"/>
-      <c r="AH394" s="1"/>
+      <c r="AH394" s="25"/>
       <c r="AI394" s="1"/>
       <c r="AJ394" s="1"/>
       <c r="AK394" s="1"/>
@@ -32577,7 +32593,7 @@
       <c r="AE395" s="1"/>
       <c r="AF395" s="1"/>
       <c r="AG395" s="1"/>
-      <c r="AH395" s="1"/>
+      <c r="AH395" s="25"/>
       <c r="AI395" s="1"/>
       <c r="AJ395" s="1"/>
       <c r="AK395" s="1"/>
@@ -32629,7 +32645,7 @@
       <c r="AE396" s="1"/>
       <c r="AF396" s="1"/>
       <c r="AG396" s="1"/>
-      <c r="AH396" s="1"/>
+      <c r="AH396" s="25"/>
       <c r="AI396" s="1"/>
       <c r="AJ396" s="1"/>
       <c r="AK396" s="1"/>
@@ -32681,7 +32697,7 @@
       <c r="AE397" s="1"/>
       <c r="AF397" s="1"/>
       <c r="AG397" s="1"/>
-      <c r="AH397" s="1"/>
+      <c r="AH397" s="25"/>
       <c r="AI397" s="1"/>
       <c r="AJ397" s="1"/>
       <c r="AK397" s="1"/>
@@ -32733,7 +32749,7 @@
       <c r="AE398" s="1"/>
       <c r="AF398" s="1"/>
       <c r="AG398" s="1"/>
-      <c r="AH398" s="1"/>
+      <c r="AH398" s="25"/>
       <c r="AI398" s="1"/>
       <c r="AJ398" s="1"/>
       <c r="AK398" s="1"/>
@@ -32785,7 +32801,7 @@
       <c r="AE399" s="1"/>
       <c r="AF399" s="1"/>
       <c r="AG399" s="1"/>
-      <c r="AH399" s="1"/>
+      <c r="AH399" s="25"/>
       <c r="AI399" s="1"/>
       <c r="AJ399" s="1"/>
       <c r="AK399" s="1"/>
@@ -32837,7 +32853,7 @@
       <c r="AE400" s="1"/>
       <c r="AF400" s="1"/>
       <c r="AG400" s="1"/>
-      <c r="AH400" s="1"/>
+      <c r="AH400" s="25"/>
       <c r="AI400" s="1"/>
       <c r="AJ400" s="1"/>
       <c r="AK400" s="1"/>
@@ -32889,7 +32905,7 @@
       <c r="AE401" s="1"/>
       <c r="AF401" s="1"/>
       <c r="AG401" s="1"/>
-      <c r="AH401" s="1"/>
+      <c r="AH401" s="25"/>
       <c r="AI401" s="1"/>
       <c r="AJ401" s="1"/>
       <c r="AK401" s="1"/>
@@ -32941,7 +32957,7 @@
       <c r="AE402" s="1"/>
       <c r="AF402" s="1"/>
       <c r="AG402" s="1"/>
-      <c r="AH402" s="1"/>
+      <c r="AH402" s="25"/>
       <c r="AI402" s="1"/>
       <c r="AJ402" s="1"/>
       <c r="AK402" s="1"/>
@@ -32993,7 +33009,7 @@
       <c r="AE403" s="1"/>
       <c r="AF403" s="1"/>
       <c r="AG403" s="1"/>
-      <c r="AH403" s="1"/>
+      <c r="AH403" s="25"/>
       <c r="AI403" s="1"/>
       <c r="AJ403" s="1"/>
       <c r="AK403" s="1"/>
@@ -33045,7 +33061,7 @@
       <c r="AE404" s="1"/>
       <c r="AF404" s="1"/>
       <c r="AG404" s="1"/>
-      <c r="AH404" s="1"/>
+      <c r="AH404" s="25"/>
       <c r="AI404" s="1"/>
       <c r="AJ404" s="1"/>
       <c r="AK404" s="1"/>
@@ -33097,7 +33113,7 @@
       <c r="AE405" s="1"/>
       <c r="AF405" s="1"/>
       <c r="AG405" s="1"/>
-      <c r="AH405" s="1"/>
+      <c r="AH405" s="25"/>
       <c r="AI405" s="1"/>
       <c r="AJ405" s="1"/>
       <c r="AK405" s="1"/>
@@ -33149,7 +33165,7 @@
       <c r="AE406" s="1"/>
       <c r="AF406" s="1"/>
       <c r="AG406" s="1"/>
-      <c r="AH406" s="1"/>
+      <c r="AH406" s="25"/>
       <c r="AI406" s="1"/>
       <c r="AJ406" s="1"/>
       <c r="AK406" s="1"/>
@@ -33201,7 +33217,7 @@
       <c r="AE407" s="1"/>
       <c r="AF407" s="1"/>
       <c r="AG407" s="1"/>
-      <c r="AH407" s="1"/>
+      <c r="AH407" s="25"/>
       <c r="AI407" s="1"/>
       <c r="AJ407" s="1"/>
       <c r="AK407" s="1"/>
@@ -33253,7 +33269,7 @@
       <c r="AE408" s="1"/>
       <c r="AF408" s="1"/>
       <c r="AG408" s="1"/>
-      <c r="AH408" s="1"/>
+      <c r="AH408" s="25"/>
       <c r="AI408" s="1"/>
       <c r="AJ408" s="1"/>
       <c r="AK408" s="1"/>
@@ -33305,7 +33321,7 @@
       <c r="AE409" s="1"/>
       <c r="AF409" s="1"/>
       <c r="AG409" s="1"/>
-      <c r="AH409" s="1"/>
+      <c r="AH409" s="25"/>
       <c r="AI409" s="1"/>
       <c r="AJ409" s="1"/>
       <c r="AK409" s="1"/>
@@ -33357,7 +33373,7 @@
       <c r="AE410" s="1"/>
       <c r="AF410" s="1"/>
       <c r="AG410" s="1"/>
-      <c r="AH410" s="1"/>
+      <c r="AH410" s="25"/>
       <c r="AI410" s="1"/>
       <c r="AJ410" s="1"/>
       <c r="AK410" s="1"/>
@@ -33409,7 +33425,7 @@
       <c r="AE411" s="1"/>
       <c r="AF411" s="1"/>
       <c r="AG411" s="1"/>
-      <c r="AH411" s="1"/>
+      <c r="AH411" s="25"/>
       <c r="AI411" s="1"/>
       <c r="AJ411" s="1"/>
       <c r="AK411" s="1"/>
@@ -33461,7 +33477,7 @@
       <c r="AE412" s="1"/>
       <c r="AF412" s="1"/>
       <c r="AG412" s="1"/>
-      <c r="AH412" s="1"/>
+      <c r="AH412" s="25"/>
       <c r="AI412" s="1"/>
       <c r="AJ412" s="1"/>
       <c r="AK412" s="1"/>
@@ -33513,7 +33529,7 @@
       <c r="AE413" s="1"/>
       <c r="AF413" s="1"/>
       <c r="AG413" s="1"/>
-      <c r="AH413" s="1"/>
+      <c r="AH413" s="25"/>
       <c r="AI413" s="1"/>
       <c r="AJ413" s="1"/>
       <c r="AK413" s="1"/>
@@ -33565,7 +33581,7 @@
       <c r="AE414" s="1"/>
       <c r="AF414" s="1"/>
       <c r="AG414" s="1"/>
-      <c r="AH414" s="1"/>
+      <c r="AH414" s="25"/>
       <c r="AI414" s="1"/>
       <c r="AJ414" s="1"/>
       <c r="AK414" s="1"/>
@@ -33617,7 +33633,7 @@
       <c r="AE415" s="1"/>
       <c r="AF415" s="1"/>
       <c r="AG415" s="1"/>
-      <c r="AH415" s="1"/>
+      <c r="AH415" s="25"/>
       <c r="AI415" s="1"/>
       <c r="AJ415" s="1"/>
       <c r="AK415" s="1"/>
@@ -33669,7 +33685,7 @@
       <c r="AE416" s="1"/>
       <c r="AF416" s="1"/>
       <c r="AG416" s="1"/>
-      <c r="AH416" s="1"/>
+      <c r="AH416" s="25"/>
       <c r="AI416" s="1"/>
       <c r="AJ416" s="1"/>
       <c r="AK416" s="1"/>
@@ -33721,7 +33737,7 @@
       <c r="AE417" s="1"/>
       <c r="AF417" s="1"/>
       <c r="AG417" s="1"/>
-      <c r="AH417" s="1"/>
+      <c r="AH417" s="25"/>
       <c r="AI417" s="1"/>
       <c r="AJ417" s="1"/>
       <c r="AK417" s="1"/>
@@ -33773,7 +33789,7 @@
       <c r="AE418" s="1"/>
       <c r="AF418" s="1"/>
       <c r="AG418" s="1"/>
-      <c r="AH418" s="1"/>
+      <c r="AH418" s="25"/>
       <c r="AI418" s="1"/>
       <c r="AJ418" s="1"/>
       <c r="AK418" s="1"/>
@@ -33825,7 +33841,7 @@
       <c r="AE419" s="1"/>
       <c r="AF419" s="1"/>
       <c r="AG419" s="1"/>
-      <c r="AH419" s="1"/>
+      <c r="AH419" s="25"/>
       <c r="AI419" s="1"/>
       <c r="AJ419" s="1"/>
       <c r="AK419" s="1"/>
@@ -33877,7 +33893,7 @@
       <c r="AE420" s="1"/>
       <c r="AF420" s="1"/>
       <c r="AG420" s="1"/>
-      <c r="AH420" s="1"/>
+      <c r="AH420" s="25"/>
       <c r="AI420" s="1"/>
       <c r="AJ420" s="1"/>
       <c r="AK420" s="1"/>
@@ -33929,7 +33945,7 @@
       <c r="AE421" s="1"/>
       <c r="AF421" s="1"/>
       <c r="AG421" s="1"/>
-      <c r="AH421" s="1"/>
+      <c r="AH421" s="25"/>
       <c r="AI421" s="1"/>
       <c r="AJ421" s="1"/>
       <c r="AK421" s="1"/>
@@ -33981,7 +33997,7 @@
       <c r="AE422" s="1"/>
       <c r="AF422" s="1"/>
       <c r="AG422" s="1"/>
-      <c r="AH422" s="1"/>
+      <c r="AH422" s="25"/>
       <c r="AI422" s="1"/>
       <c r="AJ422" s="1"/>
       <c r="AK422" s="1"/>
@@ -34033,7 +34049,7 @@
       <c r="AE423" s="1"/>
       <c r="AF423" s="1"/>
       <c r="AG423" s="1"/>
-      <c r="AH423" s="1"/>
+      <c r="AH423" s="25"/>
       <c r="AI423" s="1"/>
       <c r="AJ423" s="1"/>
       <c r="AK423" s="1"/>
@@ -34085,7 +34101,7 @@
       <c r="AE424" s="1"/>
       <c r="AF424" s="1"/>
       <c r="AG424" s="1"/>
-      <c r="AH424" s="1"/>
+      <c r="AH424" s="25"/>
       <c r="AI424" s="1"/>
       <c r="AJ424" s="1"/>
       <c r="AK424" s="1"/>
@@ -34137,7 +34153,7 @@
       <c r="AE425" s="1"/>
       <c r="AF425" s="1"/>
       <c r="AG425" s="1"/>
-      <c r="AH425" s="1"/>
+      <c r="AH425" s="25"/>
       <c r="AI425" s="1"/>
       <c r="AJ425" s="1"/>
       <c r="AK425" s="1"/>
@@ -34189,7 +34205,7 @@
       <c r="AE426" s="1"/>
       <c r="AF426" s="1"/>
       <c r="AG426" s="1"/>
-      <c r="AH426" s="1"/>
+      <c r="AH426" s="25"/>
       <c r="AI426" s="1"/>
       <c r="AJ426" s="1"/>
       <c r="AK426" s="1"/>
@@ -34241,7 +34257,7 @@
       <c r="AE427" s="1"/>
       <c r="AF427" s="1"/>
       <c r="AG427" s="1"/>
-      <c r="AH427" s="1"/>
+      <c r="AH427" s="25"/>
       <c r="AI427" s="1"/>
       <c r="AJ427" s="1"/>
       <c r="AK427" s="1"/>
@@ -34293,7 +34309,7 @@
       <c r="AE428" s="1"/>
       <c r="AF428" s="1"/>
       <c r="AG428" s="1"/>
-      <c r="AH428" s="1"/>
+      <c r="AH428" s="25"/>
       <c r="AI428" s="1"/>
       <c r="AJ428" s="1"/>
       <c r="AK428" s="1"/>
@@ -34345,7 +34361,7 @@
       <c r="AE429" s="1"/>
       <c r="AF429" s="1"/>
       <c r="AG429" s="1"/>
-      <c r="AH429" s="1"/>
+      <c r="AH429" s="25"/>
       <c r="AI429" s="1"/>
       <c r="AJ429" s="1"/>
       <c r="AK429" s="1"/>
@@ -34397,7 +34413,7 @@
       <c r="AE430" s="1"/>
       <c r="AF430" s="1"/>
       <c r="AG430" s="1"/>
-      <c r="AH430" s="1"/>
+      <c r="AH430" s="25"/>
       <c r="AI430" s="1"/>
       <c r="AJ430" s="1"/>
       <c r="AK430" s="1"/>
@@ -34449,7 +34465,7 @@
       <c r="AE431" s="1"/>
       <c r="AF431" s="1"/>
       <c r="AG431" s="1"/>
-      <c r="AH431" s="1"/>
+      <c r="AH431" s="25"/>
       <c r="AI431" s="1"/>
       <c r="AJ431" s="1"/>
       <c r="AK431" s="1"/>
@@ -34501,7 +34517,7 @@
       <c r="AE432" s="1"/>
       <c r="AF432" s="1"/>
       <c r="AG432" s="1"/>
-      <c r="AH432" s="1"/>
+      <c r="AH432" s="25"/>
       <c r="AI432" s="1"/>
       <c r="AJ432" s="1"/>
       <c r="AK432" s="1"/>
@@ -34553,7 +34569,7 @@
       <c r="AE433" s="1"/>
       <c r="AF433" s="1"/>
       <c r="AG433" s="1"/>
-      <c r="AH433" s="1"/>
+      <c r="AH433" s="25"/>
       <c r="AI433" s="1"/>
       <c r="AJ433" s="1"/>
       <c r="AK433" s="1"/>
@@ -34605,7 +34621,7 @@
       <c r="AE434" s="1"/>
       <c r="AF434" s="1"/>
       <c r="AG434" s="1"/>
-      <c r="AH434" s="1"/>
+      <c r="AH434" s="25"/>
       <c r="AI434" s="1"/>
       <c r="AJ434" s="1"/>
       <c r="AK434" s="1"/>
@@ -34657,7 +34673,7 @@
       <c r="AE435" s="1"/>
       <c r="AF435" s="1"/>
       <c r="AG435" s="1"/>
-      <c r="AH435" s="1"/>
+      <c r="AH435" s="25"/>
       <c r="AI435" s="1"/>
       <c r="AJ435" s="1"/>
       <c r="AK435" s="1"/>
@@ -34709,7 +34725,7 @@
       <c r="AE436" s="1"/>
       <c r="AF436" s="1"/>
       <c r="AG436" s="1"/>
-      <c r="AH436" s="1"/>
+      <c r="AH436" s="25"/>
       <c r="AI436" s="1"/>
       <c r="AJ436" s="1"/>
       <c r="AK436" s="1"/>
@@ -34761,7 +34777,7 @@
       <c r="AE437" s="1"/>
       <c r="AF437" s="1"/>
       <c r="AG437" s="1"/>
-      <c r="AH437" s="1"/>
+      <c r="AH437" s="25"/>
       <c r="AI437" s="1"/>
       <c r="AJ437" s="1"/>
       <c r="AK437" s="1"/>
@@ -34813,7 +34829,7 @@
       <c r="AE438" s="1"/>
       <c r="AF438" s="1"/>
       <c r="AG438" s="1"/>
-      <c r="AH438" s="1"/>
+      <c r="AH438" s="25"/>
       <c r="AI438" s="1"/>
       <c r="AJ438" s="1"/>
       <c r="AK438" s="1"/>
@@ -34865,7 +34881,7 @@
       <c r="AE439" s="1"/>
       <c r="AF439" s="1"/>
       <c r="AG439" s="1"/>
-      <c r="AH439" s="1"/>
+      <c r="AH439" s="25"/>
       <c r="AI439" s="1"/>
       <c r="AJ439" s="1"/>
       <c r="AK439" s="1"/>
@@ -34917,7 +34933,7 @@
       <c r="AE440" s="1"/>
       <c r="AF440" s="1"/>
       <c r="AG440" s="1"/>
-      <c r="AH440" s="1"/>
+      <c r="AH440" s="25"/>
       <c r="AI440" s="1"/>
       <c r="AJ440" s="1"/>
       <c r="AK440" s="1"/>
@@ -34969,7 +34985,7 @@
       <c r="AE441" s="1"/>
       <c r="AF441" s="1"/>
       <c r="AG441" s="1"/>
-      <c r="AH441" s="1"/>
+      <c r="AH441" s="25"/>
       <c r="AI441" s="1"/>
       <c r="AJ441" s="1"/>
       <c r="AK441" s="1"/>
@@ -35021,7 +35037,7 @@
       <c r="AE442" s="1"/>
       <c r="AF442" s="1"/>
       <c r="AG442" s="1"/>
-      <c r="AH442" s="1"/>
+      <c r="AH442" s="25"/>
       <c r="AI442" s="1"/>
       <c r="AJ442" s="1"/>
       <c r="AK442" s="1"/>
@@ -35073,7 +35089,7 @@
       <c r="AE443" s="1"/>
       <c r="AF443" s="1"/>
       <c r="AG443" s="1"/>
-      <c r="AH443" s="1"/>
+      <c r="AH443" s="25"/>
       <c r="AI443" s="1"/>
       <c r="AJ443" s="1"/>
       <c r="AK443" s="1"/>
@@ -35125,7 +35141,7 @@
       <c r="AE444" s="1"/>
       <c r="AF444" s="1"/>
       <c r="AG444" s="1"/>
-      <c r="AH444" s="1"/>
+      <c r="AH444" s="25"/>
       <c r="AI444" s="1"/>
       <c r="AJ444" s="1"/>
       <c r="AK444" s="1"/>
@@ -35177,7 +35193,7 @@
       <c r="AE445" s="1"/>
       <c r="AF445" s="1"/>
       <c r="AG445" s="1"/>
-      <c r="AH445" s="1"/>
+      <c r="AH445" s="25"/>
       <c r="AI445" s="1"/>
       <c r="AJ445" s="1"/>
       <c r="AK445" s="1"/>
@@ -35229,7 +35245,7 @@
       <c r="AE446" s="1"/>
       <c r="AF446" s="1"/>
       <c r="AG446" s="1"/>
-      <c r="AH446" s="1"/>
+      <c r="AH446" s="25"/>
       <c r="AI446" s="1"/>
       <c r="AJ446" s="1"/>
       <c r="AK446" s="1"/>
@@ -35281,7 +35297,7 @@
       <c r="AE447" s="1"/>
       <c r="AF447" s="1"/>
       <c r="AG447" s="1"/>
-      <c r="AH447" s="1"/>
+      <c r="AH447" s="25"/>
       <c r="AI447" s="1"/>
       <c r="AJ447" s="1"/>
       <c r="AK447" s="1"/>
@@ -35333,7 +35349,7 @@
       <c r="AE448" s="1"/>
       <c r="AF448" s="1"/>
       <c r="AG448" s="1"/>
-      <c r="AH448" s="1"/>
+      <c r="AH448" s="25"/>
       <c r="AI448" s="1"/>
       <c r="AJ448" s="1"/>
       <c r="AK448" s="1"/>
@@ -35385,7 +35401,7 @@
       <c r="AE449" s="1"/>
       <c r="AF449" s="1"/>
       <c r="AG449" s="1"/>
-      <c r="AH449" s="1"/>
+      <c r="AH449" s="25"/>
       <c r="AI449" s="1"/>
       <c r="AJ449" s="1"/>
       <c r="AK449" s="1"/>
@@ -35437,7 +35453,7 @@
       <c r="AE450" s="1"/>
       <c r="AF450" s="1"/>
       <c r="AG450" s="1"/>
-      <c r="AH450" s="1"/>
+      <c r="AH450" s="25"/>
       <c r="AI450" s="1"/>
       <c r="AJ450" s="1"/>
       <c r="AK450" s="1"/>
@@ -35489,7 +35505,7 @@
       <c r="AE451" s="1"/>
       <c r="AF451" s="1"/>
       <c r="AG451" s="1"/>
-      <c r="AH451" s="1"/>
+      <c r="AH451" s="25"/>
       <c r="AI451" s="1"/>
       <c r="AJ451" s="1"/>
       <c r="AK451" s="1"/>
@@ -35541,7 +35557,7 @@
       <c r="AE452" s="1"/>
       <c r="AF452" s="1"/>
       <c r="AG452" s="1"/>
-      <c r="AH452" s="1"/>
+      <c r="AH452" s="25"/>
       <c r="AI452" s="1"/>
       <c r="AJ452" s="1"/>
       <c r="AK452" s="1"/>
@@ -35593,7 +35609,7 @@
       <c r="AE453" s="1"/>
       <c r="AF453" s="1"/>
       <c r="AG453" s="1"/>
-      <c r="AH453" s="1"/>
+      <c r="AH453" s="25"/>
       <c r="AI453" s="1"/>
       <c r="AJ453" s="1"/>
       <c r="AK453" s="1"/>
@@ -35645,7 +35661,7 @@
       <c r="AE454" s="1"/>
       <c r="AF454" s="1"/>
       <c r="AG454" s="1"/>
-      <c r="AH454" s="1"/>
+      <c r="AH454" s="25"/>
       <c r="AI454" s="1"/>
       <c r="AJ454" s="1"/>
       <c r="AK454" s="1"/>
@@ -35697,7 +35713,7 @@
       <c r="AE455" s="1"/>
       <c r="AF455" s="1"/>
       <c r="AG455" s="1"/>
-      <c r="AH455" s="1"/>
+      <c r="AH455" s="25"/>
       <c r="AI455" s="1"/>
       <c r="AJ455" s="1"/>
       <c r="AK455" s="1"/>
@@ -35749,7 +35765,7 @@
       <c r="AE456" s="1"/>
       <c r="AF456" s="1"/>
       <c r="AG456" s="1"/>
-      <c r="AH456" s="1"/>
+      <c r="AH456" s="25"/>
       <c r="AI456" s="1"/>
       <c r="AJ456" s="1"/>
       <c r="AK456" s="1"/>
@@ -35801,7 +35817,7 @@
       <c r="AE457" s="1"/>
       <c r="AF457" s="1"/>
       <c r="AG457" s="1"/>
-      <c r="AH457" s="1"/>
+      <c r="AH457" s="25"/>
       <c r="AI457" s="1"/>
       <c r="AJ457" s="1"/>
       <c r="AK457" s="1"/>
@@ -35853,7 +35869,7 @@
       <c r="AE458" s="1"/>
       <c r="AF458" s="1"/>
       <c r="AG458" s="1"/>
-      <c r="AH458" s="1"/>
+      <c r="AH458" s="25"/>
       <c r="AI458" s="1"/>
       <c r="AJ458" s="1"/>
       <c r="AK458" s="1"/>
@@ -35905,7 +35921,7 @@
       <c r="AE459" s="1"/>
       <c r="AF459" s="1"/>
       <c r="AG459" s="1"/>
-      <c r="AH459" s="1"/>
+      <c r="AH459" s="25"/>
       <c r="AI459" s="1"/>
       <c r="AJ459" s="1"/>
       <c r="AK459" s="1"/>
@@ -35957,7 +35973,7 @@
       <c r="AE460" s="1"/>
       <c r="AF460" s="1"/>
       <c r="AG460" s="1"/>
-      <c r="AH460" s="1"/>
+      <c r="AH460" s="25"/>
       <c r="AI460" s="1"/>
       <c r="AJ460" s="1"/>
       <c r="AK460" s="1"/>
@@ -36009,7 +36025,7 @@
       <c r="AE461" s="1"/>
       <c r="AF461" s="1"/>
       <c r="AG461" s="1"/>
-      <c r="AH461" s="1"/>
+      <c r="AH461" s="25"/>
       <c r="AI461" s="1"/>
       <c r="AJ461" s="1"/>
       <c r="AK461" s="1"/>
@@ -36061,7 +36077,7 @@
       <c r="AE462" s="1"/>
       <c r="AF462" s="1"/>
       <c r="AG462" s="1"/>
-      <c r="AH462" s="1"/>
+      <c r="AH462" s="25"/>
       <c r="AI462" s="1"/>
       <c r="AJ462" s="1"/>
       <c r="AK462" s="1"/>
@@ -36113,7 +36129,7 @@
       <c r="AE463" s="1"/>
       <c r="AF463" s="1"/>
       <c r="AG463" s="1"/>
-      <c r="AH463" s="1"/>
+      <c r="AH463" s="25"/>
       <c r="AI463" s="1"/>
       <c r="AJ463" s="1"/>
       <c r="AK463" s="1"/>
@@ -36165,7 +36181,7 @@
       <c r="AE464" s="1"/>
       <c r="AF464" s="1"/>
       <c r="AG464" s="1"/>
-      <c r="AH464" s="1"/>
+      <c r="AH464" s="25"/>
       <c r="AI464" s="1"/>
       <c r="AJ464" s="1"/>
       <c r="AK464" s="1"/>
@@ -36217,7 +36233,7 @@
       <c r="AE465" s="1"/>
       <c r="AF465" s="1"/>
       <c r="AG465" s="1"/>
-      <c r="AH465" s="1"/>
+      <c r="AH465" s="25"/>
       <c r="AI465" s="1"/>
       <c r="AJ465" s="1"/>
       <c r="AK465" s="1"/>
@@ -36269,7 +36285,7 @@
       <c r="AE466" s="1"/>
       <c r="AF466" s="1"/>
       <c r="AG466" s="1"/>
-      <c r="AH466" s="1"/>
+      <c r="AH466" s="25"/>
       <c r="AI466" s="1"/>
       <c r="AJ466" s="1"/>
       <c r="AK466" s="1"/>
@@ -36321,7 +36337,7 @@
       <c r="AE467" s="1"/>
       <c r="AF467" s="1"/>
       <c r="AG467" s="1"/>
-      <c r="AH467" s="1"/>
+      <c r="AH467" s="25"/>
       <c r="AI467" s="1"/>
       <c r="AJ467" s="1"/>
       <c r="AK467" s="1"/>
@@ -36373,7 +36389,7 @@
       <c r="AE468" s="1"/>
       <c r="AF468" s="1"/>
       <c r="AG468" s="1"/>
-      <c r="AH468" s="1"/>
+      <c r="AH468" s="25"/>
       <c r="AI468" s="1"/>
       <c r="AJ468" s="1"/>
       <c r="AK468" s="1"/>
@@ -36425,7 +36441,7 @@
       <c r="AE469" s="1"/>
       <c r="AF469" s="1"/>
       <c r="AG469" s="1"/>
-      <c r="AH469" s="1"/>
+      <c r="AH469" s="25"/>
       <c r="AI469" s="1"/>
       <c r="AJ469" s="1"/>
       <c r="AK469" s="1"/>
@@ -36477,7 +36493,7 @@
       <c r="AE470" s="1"/>
       <c r="AF470" s="1"/>
       <c r="AG470" s="1"/>
-      <c r="AH470" s="1"/>
+      <c r="AH470" s="25"/>
       <c r="AI470" s="1"/>
       <c r="AJ470" s="1"/>
       <c r="AK470" s="1"/>
@@ -36529,7 +36545,7 @@
       <c r="AE471" s="1"/>
       <c r="AF471" s="1"/>
       <c r="AG471" s="1"/>
-      <c r="AH471" s="1"/>
+      <c r="AH471" s="25"/>
       <c r="AI471" s="1"/>
       <c r="AJ471" s="1"/>
       <c r="AK471" s="1"/>
@@ -36581,7 +36597,7 @@
       <c r="AE472" s="1"/>
       <c r="AF472" s="1"/>
       <c r="AG472" s="1"/>
-      <c r="AH472" s="1"/>
+      <c r="AH472" s="25"/>
       <c r="AI472" s="1"/>
       <c r="AJ472" s="1"/>
       <c r="AK472" s="1"/>
@@ -36633,7 +36649,7 @@
       <c r="AE473" s="1"/>
       <c r="AF473" s="1"/>
       <c r="AG473" s="1"/>
-      <c r="AH473" s="1"/>
+      <c r="AH473" s="25"/>
       <c r="AI473" s="1"/>
       <c r="AJ473" s="1"/>
       <c r="AK473" s="1"/>
@@ -36685,7 +36701,7 @@
       <c r="AE474" s="1"/>
       <c r="AF474" s="1"/>
       <c r="AG474" s="1"/>
-      <c r="AH474" s="1"/>
+      <c r="AH474" s="25"/>
       <c r="AI474" s="1"/>
       <c r="AJ474" s="1"/>
       <c r="AK474" s="1"/>
@@ -36737,7 +36753,7 @@
       <c r="AE475" s="1"/>
       <c r="AF475" s="1"/>
       <c r="AG475" s="1"/>
-      <c r="AH475" s="1"/>
+      <c r="AH475" s="25"/>
       <c r="AI475" s="1"/>
       <c r="AJ475" s="1"/>
       <c r="AK475" s="1"/>
@@ -36789,7 +36805,7 @@
       <c r="AE476" s="1"/>
       <c r="AF476" s="1"/>
       <c r="AG476" s="1"/>
-      <c r="AH476" s="1"/>
+      <c r="AH476" s="25"/>
       <c r="AI476" s="1"/>
       <c r="AJ476" s="1"/>
       <c r="AK476" s="1"/>
@@ -36841,7 +36857,7 @@
       <c r="AE477" s="1"/>
       <c r="AF477" s="1"/>
       <c r="AG477" s="1"/>
-      <c r="AH477" s="1"/>
+      <c r="AH477" s="25"/>
       <c r="AI477" s="1"/>
       <c r="AJ477" s="1"/>
       <c r="AK477" s="1"/>
@@ -36893,7 +36909,7 @@
       <c r="AE478" s="1"/>
       <c r="AF478" s="1"/>
       <c r="AG478" s="1"/>
-      <c r="AH478" s="1"/>
+      <c r="AH478" s="25"/>
       <c r="AI478" s="1"/>
       <c r="AJ478" s="1"/>
       <c r="AK478" s="1"/>
@@ -36945,7 +36961,7 @@
       <c r="AE479" s="1"/>
       <c r="AF479" s="1"/>
       <c r="AG479" s="1"/>
-      <c r="AH479" s="1"/>
+      <c r="AH479" s="25"/>
       <c r="AI479" s="1"/>
       <c r="AJ479" s="1"/>
       <c r="AK479" s="1"/>
@@ -36997,7 +37013,7 @@
       <c r="AE480" s="1"/>
       <c r="AF480" s="1"/>
       <c r="AG480" s="1"/>
-      <c r="AH480" s="1"/>
+      <c r="AH480" s="25"/>
       <c r="AI480" s="1"/>
       <c r="AJ480" s="1"/>
       <c r="AK480" s="1"/>
@@ -37049,7 +37065,7 @@
       <c r="AE481" s="1"/>
       <c r="AF481" s="1"/>
       <c r="AG481" s="1"/>
-      <c r="AH481" s="1"/>
+      <c r="AH481" s="25"/>
       <c r="AI481" s="1"/>
       <c r="AJ481" s="1"/>
       <c r="AK481" s="1"/>
@@ -37101,7 +37117,7 @@
       <c r="AE482" s="1"/>
       <c r="AF482" s="1"/>
       <c r="AG482" s="1"/>
-      <c r="AH482" s="1"/>
+      <c r="AH482" s="25"/>
       <c r="AI482" s="1"/>
       <c r="AJ482" s="1"/>
       <c r="AK482" s="1"/>
@@ -37153,7 +37169,7 @@
       <c r="AE483" s="1"/>
       <c r="AF483" s="1"/>
       <c r="AG483" s="1"/>
-      <c r="AH483" s="1"/>
+      <c r="AH483" s="25"/>
       <c r="AI483" s="1"/>
       <c r="AJ483" s="1"/>
       <c r="AK483" s="1"/>
@@ -37205,7 +37221,7 @@
       <c r="AE484" s="1"/>
       <c r="AF484" s="1"/>
       <c r="AG484" s="1"/>
-      <c r="AH484" s="1"/>
+      <c r="AH484" s="25"/>
       <c r="AI484" s="1"/>
       <c r="AJ484" s="1"/>
       <c r="AK484" s="1"/>
@@ -37257,7 +37273,7 @@
       <c r="AE485" s="1"/>
       <c r="AF485" s="1"/>
       <c r="AG485" s="1"/>
-      <c r="AH485" s="1"/>
+      <c r="AH485" s="25"/>
       <c r="AI485" s="1"/>
       <c r="AJ485" s="1"/>
       <c r="AK485" s="1"/>
@@ -37309,7 +37325,7 @@
       <c r="AE486" s="1"/>
       <c r="AF486" s="1"/>
       <c r="AG486" s="1"/>
-      <c r="AH486" s="1"/>
+      <c r="AH486" s="25"/>
       <c r="AI486" s="1"/>
       <c r="AJ486" s="1"/>
       <c r="AK486" s="1"/>
@@ -37361,7 +37377,7 @@
       <c r="AE487" s="1"/>
       <c r="AF487" s="1"/>
       <c r="AG487" s="1"/>
-      <c r="AH487" s="1"/>
+      <c r="AH487" s="25"/>
       <c r="AI487" s="1"/>
       <c r="AJ487" s="1"/>
       <c r="AK487" s="1"/>
@@ -37413,7 +37429,7 @@
       <c r="AE488" s="1"/>
       <c r="AF488" s="1"/>
       <c r="AG488" s="1"/>
-      <c r="AH488" s="1"/>
+      <c r="AH488" s="25"/>
       <c r="AI488" s="1"/>
       <c r="AJ488" s="1"/>
       <c r="AK488" s="1"/>
@@ -37465,7 +37481,7 @@
       <c r="AE489" s="1"/>
       <c r="AF489" s="1"/>
       <c r="AG489" s="1"/>
-      <c r="AH489" s="1"/>
+      <c r="AH489" s="25"/>
       <c r="AI489" s="1"/>
       <c r="AJ489" s="1"/>
       <c r="AK489" s="1"/>
@@ -37517,7 +37533,7 @@
       <c r="AE490" s="1"/>
       <c r="AF490" s="1"/>
       <c r="AG490" s="1"/>
-      <c r="AH490" s="1"/>
+      <c r="AH490" s="25"/>
       <c r="AI490" s="1"/>
       <c r="AJ490" s="1"/>
       <c r="AK490" s="1"/>
@@ -37569,7 +37585,7 @@
       <c r="AE491" s="1"/>
       <c r="AF491" s="1"/>
       <c r="AG491" s="1"/>
-      <c r="AH491" s="1"/>
+      <c r="AH491" s="25"/>
       <c r="AI491" s="1"/>
       <c r="AJ491" s="1"/>
       <c r="AK491" s="1"/>
@@ -37621,7 +37637,7 @@
       <c r="AE492" s="1"/>
       <c r="AF492" s="1"/>
       <c r="AG492" s="1"/>
-      <c r="AH492" s="1"/>
+      <c r="AH492" s="25"/>
       <c r="AI492" s="1"/>
       <c r="AJ492" s="1"/>
       <c r="AK492" s="1"/>
@@ -37673,7 +37689,7 @@
       <c r="AE493" s="1"/>
       <c r="AF493" s="1"/>
       <c r="AG493" s="1"/>
-      <c r="AH493" s="1"/>
+      <c r="AH493" s="25"/>
       <c r="AI493" s="1"/>
       <c r="AJ493" s="1"/>
       <c r="AK493" s="1"/>
@@ -37725,7 +37741,7 @@
       <c r="AE494" s="1"/>
       <c r="AF494" s="1"/>
       <c r="AG494" s="1"/>
-      <c r="AH494" s="1"/>
+      <c r="AH494" s="25"/>
       <c r="AI494" s="1"/>
       <c r="AJ494" s="1"/>
       <c r="AK494" s="1"/>
@@ -37777,7 +37793,7 @@
       <c r="AE495" s="1"/>
       <c r="AF495" s="1"/>
       <c r="AG495" s="1"/>
-      <c r="AH495" s="1"/>
+      <c r="AH495" s="25"/>
       <c r="AI495" s="1"/>
       <c r="AJ495" s="1"/>
       <c r="AK495" s="1"/>
@@ -37829,7 +37845,7 @@
       <c r="AE496" s="1"/>
       <c r="AF496" s="1"/>
       <c r="AG496" s="1"/>
-      <c r="AH496" s="1"/>
+      <c r="AH496" s="25"/>
       <c r="AI496" s="1"/>
       <c r="AJ496" s="1"/>
       <c r="AK496" s="1"/>
@@ -37881,7 +37897,7 @@
       <c r="AE497" s="1"/>
       <c r="AF497" s="1"/>
       <c r="AG497" s="1"/>
-      <c r="AH497" s="1"/>
+      <c r="AH497" s="25"/>
       <c r="AI497" s="1"/>
       <c r="AJ497" s="1"/>
       <c r="AK497" s="1"/>
@@ -37933,7 +37949,7 @@
       <c r="AE498" s="1"/>
       <c r="AF498" s="1"/>
       <c r="AG498" s="1"/>
-      <c r="AH498" s="1"/>
+      <c r="AH498" s="25"/>
       <c r="AI498" s="1"/>
       <c r="AJ498" s="1"/>
       <c r="AK498" s="1"/>
@@ -37985,7 +38001,7 @@
       <c r="AE499" s="1"/>
       <c r="AF499" s="1"/>
       <c r="AG499" s="1"/>
-      <c r="AH499" s="1"/>
+      <c r="AH499" s="25"/>
       <c r="AI499" s="1"/>
       <c r="AJ499" s="1"/>
       <c r="AK499" s="1"/>
